--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_LEDHEA-CSTD-1-00-A-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_LEDHEA-CSTD-1-00-A-C0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\10_mcu\19epfv3_mcu_app_mainline\src\IpcApplication\Vom\Alert\matrix\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_JPlaptop\BEV_MCU\git_v043_AlertFix\src\PE1VM1\App\MET\IpcApplication\Vom\Alert\matrix\scc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB5EED4-DD9E-47BE-8CBC-8E9953863D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0C586C-F045-4367-968C-34122A6ECB61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7575" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14535" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙（承認欄）" sheetId="12" r:id="rId1"/>
@@ -674,7 +674,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2559" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2563" uniqueCount="307">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -2725,9 +2725,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>○</t>
-  </si>
-  <si>
     <t>ALERT_CH_B_LEDHEA</t>
   </si>
   <si>
@@ -2738,10 +2735,6 @@
   </si>
   <si>
     <t>ON</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>LHLW</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -3053,9 +3046,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>(株)NTTデータMSE</t>
-  </si>
-  <si>
     <t>承認</t>
     <rPh sb="0" eb="2">
       <t>ショウニン</t>
@@ -3196,6 +3186,34 @@
     <t>品質総点検(R4)：Alert設計書の修正対応
 [B_LEDHEA]シート
 ・数式の変更(AU10、AU11)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>DTPH Kiko</t>
+  </si>
+  <si>
+    <t>1.1.3</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>－</t>
+  </si>
+  <si>
+    <t>(株)デンソー</t>
+  </si>
+  <si>
+    <t>BEVシス検ADAS
+課題対応（BEV3CDCMET-2941）
+[Matrix]シート
+・RWの記載を変更（○→ー）
+[CH_Design]シート
+・RWの記載を変更（LHLW→ー）</t>
+    <rPh sb="11" eb="13">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>タイオウ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3569,7 +3587,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="83">
+  <borders count="85">
     <border>
       <left/>
       <right/>
@@ -4635,6 +4653,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -4647,7 +4691,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="306">
+  <cellXfs count="311">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5372,6 +5416,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5381,6 +5440,9 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5405,9 +5467,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="75" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5853,16 +5912,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>100782</xdr:colOff>
+      <xdr:colOff>134399</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>100782</xdr:rowOff>
+      <xdr:rowOff>103957</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
+        <xdr:cNvPr id="7" name="図 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EC33A4F-8A82-449D-93AA-1F2571532C4F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B6DB257-AE09-FB9D-580E-20F211458FEB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5878,8 +5937,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5667375" y="8420100"/>
-          <a:ext cx="586557" cy="586557"/>
+          <a:off x="5098676" y="8157882"/>
+          <a:ext cx="571429" cy="571429"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10440,17 +10499,17 @@
       <sheetName val="４．ナビモデル"/>
       <sheetName val="３．サウンドモデル"/>
       <sheetName val="２．ラジオモデル"/>
+      <sheetName val="1.概述"/>
       <sheetName val="V200複合試験_担当分け_(2)1"/>
       <sheetName val="Spec_List_(19MC-DCM)_1"/>
       <sheetName val="Cooling_Unit"/>
-      <sheetName val="1.概述"/>
       <sheetName val="OpenIssueList"/>
-      <sheetName val="PullDown"/>
       <sheetName val="ECU基盤"/>
       <sheetName val="Name2"/>
       <sheetName val="Name3"/>
       <sheetName val="Company"/>
       <sheetName val="Name"/>
+      <sheetName val="PullDown"/>
       <sheetName val="エンジン型式"/>
       <sheetName val="分类数据"/>
       <sheetName val="index"/>
@@ -10482,6 +10541,37 @@
       <sheetName val="改訂履歴"/>
       <sheetName val="Sheet1"/>
       <sheetName val="⑥フューエル"/>
+      <sheetName val="STEP1-Definition"/>
+      <sheetName val="No.31"/>
+      <sheetName val="階層一覧"/>
+      <sheetName val="测试计划"/>
+      <sheetName val="2.2.4_起動終了時"/>
+      <sheetName val="全戻りﾊﾞｸﾞ"/>
+      <sheetName val="DataShare"/>
+      <sheetName val="ＯＰＭ設備"/>
+      <sheetName val="償却計算"/>
+      <sheetName val="技術費"/>
+      <sheetName val="消耗材"/>
+      <sheetName val="生産用消耗工具費"/>
+      <sheetName val="投資込みＭＪ原価"/>
+      <sheetName val="ＭＪ加工費"/>
+      <sheetName val="仕損根拠"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="ERRＩＤ90"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="RGB"/>
+      <sheetName val="調査シート"/>
+      <sheetName val="SCH"/>
+      <sheetName val="发行控制"/>
+      <sheetName val="Vibrate test"/>
+      <sheetName val="Data"/>
+      <sheetName val="注釈"/>
+      <sheetName val="仕向け決定用情報取得(GM250)"/>
+      <sheetName val="付録①（GM用）"/>
+      <sheetName val="Data.Share"/>
+      <sheetName val="Func.Share"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -10562,10 +10652,10 @@
       <sheetData sheetId="57" refreshError="1"/>
       <sheetData sheetId="58" refreshError="1"/>
       <sheetData sheetId="59" refreshError="1"/>
-      <sheetData sheetId="60"/>
+      <sheetData sheetId="60" refreshError="1"/>
       <sheetData sheetId="61"/>
       <sheetData sheetId="62"/>
-      <sheetData sheetId="63" refreshError="1"/>
+      <sheetData sheetId="63"/>
       <sheetData sheetId="64" refreshError="1"/>
       <sheetData sheetId="65" refreshError="1"/>
       <sheetData sheetId="66" refreshError="1"/>
@@ -10604,6 +10694,37 @@
       <sheetData sheetId="99" refreshError="1"/>
       <sheetData sheetId="100" refreshError="1"/>
       <sheetData sheetId="101" refreshError="1"/>
+      <sheetData sheetId="102" refreshError="1"/>
+      <sheetData sheetId="103" refreshError="1"/>
+      <sheetData sheetId="104" refreshError="1"/>
+      <sheetData sheetId="105" refreshError="1"/>
+      <sheetData sheetId="106" refreshError="1"/>
+      <sheetData sheetId="107" refreshError="1"/>
+      <sheetData sheetId="108" refreshError="1"/>
+      <sheetData sheetId="109" refreshError="1"/>
+      <sheetData sheetId="110" refreshError="1"/>
+      <sheetData sheetId="111" refreshError="1"/>
+      <sheetData sheetId="112" refreshError="1"/>
+      <sheetData sheetId="113" refreshError="1"/>
+      <sheetData sheetId="114" refreshError="1"/>
+      <sheetData sheetId="115" refreshError="1"/>
+      <sheetData sheetId="116" refreshError="1"/>
+      <sheetData sheetId="117" refreshError="1"/>
+      <sheetData sheetId="118" refreshError="1"/>
+      <sheetData sheetId="119" refreshError="1"/>
+      <sheetData sheetId="120" refreshError="1"/>
+      <sheetData sheetId="121" refreshError="1"/>
+      <sheetData sheetId="122" refreshError="1"/>
+      <sheetData sheetId="123" refreshError="1"/>
+      <sheetData sheetId="124" refreshError="1"/>
+      <sheetData sheetId="125" refreshError="1"/>
+      <sheetData sheetId="126" refreshError="1"/>
+      <sheetData sheetId="127" refreshError="1"/>
+      <sheetData sheetId="128" refreshError="1"/>
+      <sheetData sheetId="129" refreshError="1"/>
+      <sheetData sheetId="130" refreshError="1"/>
+      <sheetData sheetId="131" refreshError="1"/>
+      <sheetData sheetId="132" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -10742,12 +10863,49 @@
       <sheetName val="Config - dspmgr"/>
       <sheetName val="凡例・注記記載用"/>
       <sheetName val="入力パラメータ"/>
-      <sheetName val="原紙"/>
       <sheetName val="マスタテーブル登録データ"/>
       <sheetName val="記入シート"/>
+      <sheetName val="原紙"/>
       <sheetName val="format"/>
       <sheetName val="検査シート"/>
       <sheetName val="1.概述"/>
+      <sheetName val="InterFace"/>
+      <sheetName val="集計表"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="RGB"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="日程"/>
+      <sheetName val="進捗"/>
+      <sheetName val="印刷"/>
+      <sheetName val="★ONS_MSG_list"/>
+      <sheetName val="Defined Layout Screen_Ver.0.6"/>
+      <sheetName val="ｲﾝﾊﾟｸﾄ影響台数集計表"/>
+      <sheetName val="実勢(売上)台数表"/>
+      <sheetName val="月別企画台数表"/>
+      <sheetName val="プロジェクト一覧表(現行)"/>
+      <sheetName val="限界利益表(半期別)"/>
+      <sheetName val="機種マスタ"/>
+      <sheetName val="機種ﾏｽﾀ（他車）"/>
+      <sheetName val="売上高表(半期別)"/>
+      <sheetName val="地点情報データ応答"/>
+      <sheetName val="階層一覧"/>
+      <sheetName val="リソーセス算出"/>
+      <sheetName val="定義"/>
+      <sheetName val="ドメイン一覧"/>
+      <sheetName val="変更区分一覧"/>
+      <sheetName val="難易度量一覧"/>
+      <sheetName val="ユーザ一覧"/>
+      <sheetName val="Normal(Mark)"/>
+      <sheetName val="リストデータ"/>
+      <sheetName val="②P071中計　工数パターン1312更新"/>
+      <sheetName val="FBtbl"/>
+      <sheetName val="R0-10表紙"/>
+      <sheetName val="入力規則"/>
+      <sheetName val="#REF"/>
+      <sheetName val="Contents"/>
+      <sheetName val="選択肢"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -10820,7 +10978,7 @@
       <sheetData sheetId="61" refreshError="1"/>
       <sheetData sheetId="62" refreshError="1"/>
       <sheetData sheetId="63" refreshError="1"/>
-      <sheetData sheetId="64" refreshError="1"/>
+      <sheetData sheetId="64"/>
       <sheetData sheetId="65" refreshError="1"/>
       <sheetData sheetId="66"/>
       <sheetData sheetId="67"/>
@@ -10835,7 +10993,7 @@
       <sheetData sheetId="76"/>
       <sheetData sheetId="77" refreshError="1"/>
       <sheetData sheetId="78" refreshError="1"/>
-      <sheetData sheetId="79" refreshError="1"/>
+      <sheetData sheetId="79"/>
       <sheetData sheetId="80"/>
       <sheetData sheetId="81" refreshError="1"/>
       <sheetData sheetId="82" refreshError="1"/>
@@ -10891,6 +11049,43 @@
       <sheetData sheetId="132" refreshError="1"/>
       <sheetData sheetId="133" refreshError="1"/>
       <sheetData sheetId="134" refreshError="1"/>
+      <sheetData sheetId="135" refreshError="1"/>
+      <sheetData sheetId="136" refreshError="1"/>
+      <sheetData sheetId="137" refreshError="1"/>
+      <sheetData sheetId="138" refreshError="1"/>
+      <sheetData sheetId="139" refreshError="1"/>
+      <sheetData sheetId="140" refreshError="1"/>
+      <sheetData sheetId="141" refreshError="1"/>
+      <sheetData sheetId="142" refreshError="1"/>
+      <sheetData sheetId="143" refreshError="1"/>
+      <sheetData sheetId="144" refreshError="1"/>
+      <sheetData sheetId="145" refreshError="1"/>
+      <sheetData sheetId="146" refreshError="1"/>
+      <sheetData sheetId="147" refreshError="1"/>
+      <sheetData sheetId="148" refreshError="1"/>
+      <sheetData sheetId="149" refreshError="1"/>
+      <sheetData sheetId="150" refreshError="1"/>
+      <sheetData sheetId="151" refreshError="1"/>
+      <sheetData sheetId="152" refreshError="1"/>
+      <sheetData sheetId="153" refreshError="1"/>
+      <sheetData sheetId="154" refreshError="1"/>
+      <sheetData sheetId="155" refreshError="1"/>
+      <sheetData sheetId="156" refreshError="1"/>
+      <sheetData sheetId="157" refreshError="1"/>
+      <sheetData sheetId="158" refreshError="1"/>
+      <sheetData sheetId="159" refreshError="1"/>
+      <sheetData sheetId="160" refreshError="1"/>
+      <sheetData sheetId="161" refreshError="1"/>
+      <sheetData sheetId="162" refreshError="1"/>
+      <sheetData sheetId="163" refreshError="1"/>
+      <sheetData sheetId="164" refreshError="1"/>
+      <sheetData sheetId="165" refreshError="1"/>
+      <sheetData sheetId="166" refreshError="1"/>
+      <sheetData sheetId="167" refreshError="1"/>
+      <sheetData sheetId="168" refreshError="1"/>
+      <sheetData sheetId="169" refreshError="1"/>
+      <sheetData sheetId="170" refreshError="1"/>
+      <sheetData sheetId="171" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -11072,10 +11267,10 @@
       <sheetName val="CPF"/>
       <sheetName val="編集"/>
       <sheetName val="PAIData"/>
+      <sheetName val="⑪1ﾊﾞﾘｴｰｼｮﾝ(16LX)△１"/>
       <sheetName val="NCastalone"/>
       <sheetName val="dongia (2)"/>
       <sheetName val="Volumes"/>
-      <sheetName val="⑪1ﾊﾞﾘｴｰｼｮﾝ(16LX)△１"/>
       <sheetName val="加工費"/>
       <sheetName val="車両仕様 嗼1嗼1噌1鲌"/>
       <sheetName val="車両仕様 勜+勜+匬+鲌"/>
@@ -11085,8 +11280,8 @@
       <sheetName val="Y230"/>
       <sheetName val="MASTER"/>
       <sheetName val="設定"/>
+      <sheetName val="電子ﾎﾞﾘｭｰﾑ設定値（740Nと同一）"/>
       <sheetName val="⑥フューエル"/>
-      <sheetName val="電子ﾎﾞﾘｭｰﾑ設定値（740Nと同一）"/>
       <sheetName val="ﾌﾟﾙﾀﾞｳﾝﾒﾆｭｰ"/>
       <sheetName val="設品表01-3-23作成"/>
       <sheetName val="wire"/>
@@ -11102,25 +11297,24 @@
       <sheetName val="610L611L品番一覧"/>
       <sheetName val="【Input】見積基礎情報（海外生産分)"/>
       <sheetName val="IM-P-L-JB "/>
-      <sheetName val="797T輸入部品リスト"/>
-      <sheetName val="テーブル"/>
-      <sheetName val="Master Updated(517)"/>
-      <sheetName val="４-２．151項目累積（日本）"/>
-      <sheetName val="５-２．151項目累積（北米）"/>
-      <sheetName val="５-１．151項目詳細（北米）"/>
-      <sheetName val="545N仕様ﾗﾌ2"/>
-      <sheetName val="商品力向上"/>
-      <sheetName val="OP-PD"/>
-      <sheetName val="６２３Ｔ"/>
+      <sheetName val="RMBSS's Triggered"/>
+      <sheetName val="_"/>
       <sheetName val="Main 2"/>
       <sheetName val="Datasheet from R. Hinds"/>
-      <sheetName val="GMT900 IPC"/>
+      <sheetName val="545N仕様ﾗﾌ2"/>
+      <sheetName val="Master Updated(517)"/>
+      <sheetName val="６２３Ｔ"/>
+      <sheetName val="商品力向上"/>
+      <sheetName val="ED AND EDOV"/>
       <sheetName val="HORAS_TRAB"/>
       <sheetName val="Resumo_Corolla"/>
       <sheetName val="GASTOS_COROLLA"/>
-      <sheetName val="CALC"/>
-      <sheetName val="ﾘｽﾄ候補"/>
-      <sheetName val="ｺｰﾄﾞ表"/>
+      <sheetName val="④要素記号一覧表"/>
+      <sheetName val="START"/>
+      <sheetName val="Blue Flag"/>
+      <sheetName val="Calc Sheet Budget"/>
+      <sheetName val="見積一覧（１案）"/>
+      <sheetName val="部品"/>
       <sheetName val="①評価項目_メーカー"/>
       <sheetName val="車両仕様_x005f_x0000_4__x005f_x0000__x005f_x0011__x00"/>
       <sheetName val="車両仕様4__x005f_x0000__x005f_x0011__x005f_x0000_"/>
@@ -11147,16 +11341,9 @@
       <sheetName val="車両仕様_4___x005f_x005f_x005f_x005f_x005f_x005f_x001"/>
       <sheetName val="車両仕様4___x005f_x005f_x005f_x005f_x005f_x005f_x0011"/>
       <sheetName val="EFFY_MAZDA"/>
-      <sheetName val="ﾌﾟﾙﾀﾞｳﾝﾒﾆｭｰ用ｺｰﾄﾞ表"/>
-      <sheetName val="_"/>
-      <sheetName val="RMBSS's Triggered"/>
-      <sheetName val="ED AND EDOV"/>
-      <sheetName val="④要素記号一覧表"/>
-      <sheetName val="START"/>
-      <sheetName val="Blue Flag"/>
-      <sheetName val="Calc Sheet Budget"/>
-      <sheetName val="見積一覧（１案）"/>
-      <sheetName val="部品"/>
+      <sheetName val="４-２．151項目累積（日本）"/>
+      <sheetName val="５-２．151項目累積（北米）"/>
+      <sheetName val="５-１．151項目詳細（北米）"/>
       <sheetName val="sebelumCR"/>
       <sheetName val="08TMME"/>
       <sheetName val="VCPT"/>
@@ -11166,6 +11353,14 @@
       <sheetName val="WIP Cal Sheet"/>
       <sheetName val="Pricing overview"/>
       <sheetName val="駆動系1"/>
+      <sheetName val="797T輸入部品リスト"/>
+      <sheetName val="テーブル"/>
+      <sheetName val="OP-PD"/>
+      <sheetName val="GMT900 IPC"/>
+      <sheetName val="CALC"/>
+      <sheetName val="ﾘｽﾄ候補"/>
+      <sheetName val="ｺｰﾄﾞ表"/>
+      <sheetName val="ﾌﾟﾙﾀﾞｳﾝﾒﾆｭｰ用ｺｰﾄﾞ表"/>
       <sheetName val="393.N"/>
       <sheetName val="CæÊ _x0015_ Op"/>
       <sheetName val="ƒƒCƒ“‰æ–Ê _x0015_ Op"/>
@@ -11185,6 +11380,10 @@
       <sheetName val="車両仕様_ᵣ逰ᵣ邀ᵣ郰ᵣ"/>
       <sheetName val="他"/>
       <sheetName val="part"/>
+      <sheetName val="415T原"/>
+      <sheetName val="PAC14"/>
+      <sheetName val="部品表"/>
+      <sheetName val="■07中期明細雛形"/>
       <sheetName val="Vectra"/>
       <sheetName val="PRADO"/>
       <sheetName val="Previous"/>
@@ -11224,10 +11423,6 @@
       <sheetName val="OTHERS x620"/>
       <sheetName val="Ref"/>
       <sheetName val="TOTAL P2"/>
-      <sheetName val="415T原"/>
-      <sheetName val="PAC14"/>
-      <sheetName val="部品表"/>
-      <sheetName val="■07中期明細雛形"/>
       <sheetName val="BUYERS"/>
       <sheetName val="Status"/>
       <sheetName val="PR"/>
@@ -12215,18 +12410,18 @@
       <sheetName val="SUM"/>
       <sheetName val="ﾄﾗｯｸ"/>
       <sheetName val="00"/>
+      <sheetName val="追加検討（調光外部出力）"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="RGB"/>
+      <sheetName val="option"/>
       <sheetName val="課題管理"/>
       <sheetName val="C-55227AB"/>
       <sheetName val="Data Definition"/>
       <sheetName val="FC_まとめる"/>
-      <sheetName val="vocabulary"/>
-      <sheetName val="Calibration"/>
-      <sheetName val="CVBS"/>
-      <sheetName val="RGB"/>
       <sheetName val="車両仕様_4___x0011__x00"/>
       <sheetName val="ドメインリスト"/>
-      <sheetName val="option"/>
-      <sheetName val="追加検討（調光外部出力）"/>
       <sheetName val="入力規則"/>
       <sheetName val="Inf"/>
       <sheetName val="#REF!"/>
@@ -12317,8 +12512,29 @@
       <sheetName val="入力LIST"/>
       <sheetName val="パラメータ一覧(AXSS.AXCS)"/>
       <sheetName val="設定値定義"/>
+      <sheetName val="リストデータ"/>
+      <sheetName val="All"/>
+      <sheetName val="58831-06360"/>
+      <sheetName val="1999.4"/>
+      <sheetName val="車両仕様 _x005f_x0000__x005f_x0000__x005f_x000a__x000"/>
+      <sheetName val="車両仕様_x005f_x0000_ῃ_x005f_x0000__x005f_x0014__x000"/>
+      <sheetName val="車両仕様_x005f_x0000__x005f_x0000__x005f_x0000__x0000"/>
+      <sheetName val="車両仕様_x005f_x0000_ῆ玐ῆꆠῨ"/>
+      <sheetName val="車両仕様4?_x005f_x0000__x005f_x0000__x005f_x0000_"/>
+      <sheetName val="SHEET  car no"/>
       <sheetName val="車両仕様????帅?"/>
       <sheetName val="Net Price Position _ Sheet 1"/>
+      <sheetName val="Packing_List2"/>
+      <sheetName val="Packing_List"/>
+      <sheetName val="Calculation_PS"/>
+      <sheetName val="Customer_behaver"/>
+      <sheetName val="Seat_Assy_Tool_Tracking"/>
+      <sheetName val="Stock_in_Trade1"/>
+      <sheetName val="Packing_List21"/>
+      <sheetName val="Packing_List1"/>
+      <sheetName val="Calculation_PS1"/>
+      <sheetName val="Customer_behaver1"/>
+      <sheetName val="Seat_Assy_Tool_Tracking1"/>
       <sheetName val="POs"/>
       <sheetName val="計算式"/>
       <sheetName val="工管合計"/>
@@ -13842,15 +14058,9 @@
       <sheetName val="5"/>
       <sheetName val="確認ｼｰﾄ(TBU)"/>
       <sheetName val="Sheet1 (2)"/>
-      <sheetName val="SHEET  car no"/>
       <sheetName val="サイクル"/>
       <sheetName val="特殊サイクル一覧"/>
       <sheetName val="カメラ"/>
-      <sheetName val="車両仕様 _x005f_x0000__x005f_x0000__x005f_x000a__x000"/>
-      <sheetName val="車両仕様_x005f_x0000_ῃ_x005f_x0000__x005f_x0014__x000"/>
-      <sheetName val="車両仕様_x005f_x0000__x005f_x0000__x005f_x0000__x0000"/>
-      <sheetName val="車両仕様_x005f_x0000_ῆ玐ῆꆠῨ"/>
-      <sheetName val="車両仕様4?_x005f_x0000__x005f_x0000__x005f_x0000_"/>
       <sheetName val="台数"/>
       <sheetName val="MET397D-25"/>
       <sheetName val="集計表"/>
@@ -13859,21 +14069,6 @@
       <sheetName val="Ｓｉ問連"/>
       <sheetName val="アップロード系(2)"/>
       <sheetName val="エンジン型式"/>
-      <sheetName val="リストデータ"/>
-      <sheetName val="All"/>
-      <sheetName val="58831-06360"/>
-      <sheetName val="1999.4"/>
-      <sheetName val="Packing_List2"/>
-      <sheetName val="Packing_List"/>
-      <sheetName val="Calculation_PS"/>
-      <sheetName val="Customer_behaver"/>
-      <sheetName val="Seat_Assy_Tool_Tracking"/>
-      <sheetName val="Stock_in_Trade1"/>
-      <sheetName val="Packing_List21"/>
-      <sheetName val="Packing_List1"/>
-      <sheetName val="Calculation_PS1"/>
-      <sheetName val="Customer_behaver1"/>
-      <sheetName val="Seat_Assy_Tool_Tracking1"/>
       <sheetName val="Index"/>
       <sheetName val="Defined Layout Screen_Ver.0.6"/>
       <sheetName val="９ｘ"/>
@@ -13885,6 +14080,185 @@
       <sheetName val="config"/>
       <sheetName val="地点情報データ応答"/>
       <sheetName val="Par"/>
+      <sheetName val="Calcul"/>
+      <sheetName val="ETC機能判定"/>
+      <sheetName val="ETCメニュー"/>
+      <sheetName val="登録情報表示"/>
+      <sheetName val="ETC設定"/>
+      <sheetName val="履歴情報表示"/>
+      <sheetName val="履歴情報詳細表示"/>
+      <sheetName val="メニュー２"/>
+      <sheetName val="割込み(Disp)"/>
+      <sheetName val="割込み(Navi)"/>
+      <sheetName val="走行強制状態変化"/>
+      <sheetName val="入力パラメータ"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="InterFace"/>
+      <sheetName val="FBtbl"/>
+      <sheetName val="リスト画面"/>
+      <sheetName val="特殊画面"/>
+      <sheetName val="入力画面"/>
+      <sheetName val="メッセージ受信開始"/>
+      <sheetName val="Mark"/>
+      <sheetName val="Contents"/>
+      <sheetName val="車両仕様4_ "/>
+      <sheetName val="改正履歴"/>
+      <sheetName val="リスト選択用"/>
+      <sheetName val="变更履历"/>
+      <sheetName val="Menu List"/>
+      <sheetName val="ドメイン一覧"/>
+      <sheetName val="検査シート"/>
+      <sheetName val="Cover"/>
+      <sheetName val="MIS REPORT "/>
+      <sheetName val="（別紙5-1）PP02簡素化"/>
+      <sheetName val="universal"/>
+      <sheetName val="Cost Casting"/>
+      <sheetName val="paint mtrl"/>
+      <sheetName val="corolla_095W_"/>
+      <sheetName val="dyna"/>
+      <sheetName val="FC"/>
+      <sheetName val="★ONS_MSG_list"/>
+      <sheetName val="ﾕｰｻﾞｰ設定"/>
+      <sheetName val="同行评审"/>
+      <sheetName val="5.心配点抽出-0"/>
+      <sheetName val="0.表紙"/>
+      <sheetName val="1._概要"/>
+      <sheetName val="4 選局"/>
+      <sheetName val="定数"/>
+      <sheetName val="Case 21_1"/>
+      <sheetName val="96期(川崎)"/>
+      <sheetName val="ORDSHP"/>
+      <sheetName val="B"/>
+      <sheetName val="Blue_Flag3"/>
+      <sheetName val="Calc_Sheet_Budget3"/>
+      <sheetName val="_PART_479W_LHD3"/>
+      <sheetName val="_PART_MYY5A3"/>
+      <sheetName val="393_N3"/>
+      <sheetName val="WIP_Cal_Sheet3"/>
+      <sheetName val="Pricing_overview3"/>
+      <sheetName val="Lookup_Table3"/>
+      <sheetName val="promo_lists_20113"/>
+      <sheetName val="車両仕様_嗼1嗼1噌1鲌3"/>
+      <sheetName val="車両仕様_勜+勜+匬+鲌3"/>
+      <sheetName val="EquipmentTrimming_Cabin_NS3"/>
+      <sheetName val="Reference_3"/>
+      <sheetName val="車両仕様__x005f_x0000__x005f_x0000_?_x005f_x0012_?瞳?3"/>
+      <sheetName val="車両仕様_???_x005f_x0012_?瞳?3"/>
+      <sheetName val="160th_NPCC_Nov'103"/>
+      <sheetName val="RMBSS's_Triggered3"/>
+      <sheetName val="車両仕様?4???_??3"/>
+      <sheetName val="車両仕様_???_?瞳?3"/>
+      <sheetName val="車両仕様???ꎨ_窉瞳㾐3"/>
+      <sheetName val="車両仕様?4??_?3"/>
+      <sheetName val="車両仕様4??_?3"/>
+      <sheetName val="車両仕様____瞳_3"/>
+      <sheetName val="車両仕様______瞳_3"/>
+      <sheetName val="車両仕様_4______3"/>
+      <sheetName val="車両仕様___ꎨ_窉瞳㾐3"/>
+      <sheetName val="車両仕様_4____3"/>
+      <sheetName val="車両仕様4____3"/>
+      <sheetName val="PRICE_LIST3"/>
+      <sheetName val="Loss_Time3"/>
+      <sheetName val="Price_range_IT3"/>
+      <sheetName val="Avensis+d_seg__in_&amp;_out_of_UK+3"/>
+      <sheetName val="#ofclose__xl3"/>
+      <sheetName val="Annexes_toutes_bases3"/>
+      <sheetName val="DON_GIA3"/>
+      <sheetName val="CHITIET_VL-NC3"/>
+      <sheetName val="TONGKE3p_3"/>
+      <sheetName val="TOTAL_P23"/>
+      <sheetName val="2_-_Summary3"/>
+      <sheetName val="IPOTESI_PIANO_STATICA3"/>
+      <sheetName val="make_up3"/>
+      <sheetName val="車両仕様_???_x005f_x005f_x005f_x0012_?瞳?3"/>
+      <sheetName val="調達担当者(06_2～)3"/>
+      <sheetName val="車両仕様__x005f_x0000__2"/>
+      <sheetName val="車両仕様_x005f_x0000__N2"/>
+      <sheetName val="車両仕様___x005f_x0012_2"/>
+      <sheetName val="車両仕様__x005f_x005f_x2"/>
+      <sheetName val="車両仕様___x005f_x005f_2"/>
+      <sheetName val="05-065_she2"/>
+      <sheetName val="idgr_-_formula2"/>
+      <sheetName val="IDGR_(3)2"/>
+      <sheetName val="IDGR_(2)2"/>
+      <sheetName val="PLIV_(3)2"/>
+      <sheetName val="PLIV_(2)2"/>
+      <sheetName val="PLIV_(template)2"/>
+      <sheetName val="inv_recon2"/>
+      <sheetName val="side_member2"/>
+      <sheetName val="TTC_(FG)2"/>
+      <sheetName val="Sheet1_(3)2"/>
+      <sheetName val="truck_allocation2"/>
+      <sheetName val="Supplier_Price_Check2"/>
+      <sheetName val="$_-_june2"/>
+      <sheetName val="Vios_Cost_Reduction_actual_pro2"/>
+      <sheetName val="RET_PALLET2"/>
+      <sheetName val="Form_A2"/>
+      <sheetName val="NG_SUMMARY2"/>
+      <sheetName val="impact_pallet_and_racks2"/>
+      <sheetName val="Daily_WSD2"/>
+      <sheetName val="ass'y_12'04-05'053"/>
+      <sheetName val="Type_I2"/>
+      <sheetName val="Schedule_PM2"/>
+      <sheetName val="training_forklift2"/>
+      <sheetName val="Budget_by_Category2"/>
+      <sheetName val="investment_tmc_v8_0_34p2"/>
+      <sheetName val="PTD_Activity2"/>
+      <sheetName val="Sample_1PP_2"/>
+      <sheetName val="Open_Ran3"/>
+      <sheetName val="Open_RAN_23"/>
+      <sheetName val="CHIA_KH2"/>
+      <sheetName val="Purch__BP2"/>
+      <sheetName val="車両仕様_____x005f_x005f_x005f_x005f_x0013"/>
+      <sheetName val="車両仕様_____x005f_x005f_x005f_x005f_x0053"/>
+      <sheetName val="ＰＲＥ_NO1"/>
+      <sheetName val="Courier_4x2"/>
+      <sheetName val="Price_Trend2"/>
+      <sheetName val="車両仕様_?_x005f_x0012_?瞳?2"/>
+      <sheetName val="YARIS_HB2"/>
+      <sheetName val="00_KS"/>
+      <sheetName val="PRADO_3Dr_fl2"/>
+      <sheetName val="01_DATA2"/>
+      <sheetName val="Quality_Update2"/>
+      <sheetName val="prior_data"/>
+      <sheetName val="Table_Master"/>
+      <sheetName val="1_概述"/>
+      <sheetName val="Drop-down_Menu_List"/>
+      <sheetName val="Open_Item_List"/>
+      <sheetName val="本修正_DIFF_"/>
+      <sheetName val="Sector_Assignment"/>
+      <sheetName val="BQ_CONVEYOR"/>
+      <sheetName val="IMV_LIST_2003"/>
+      <sheetName val="車両仕様_x005f_x0000_4__x005f_x0000__x005f_x0000___x0"/>
+      <sheetName val="車両仕様__x005f_x0000__x005f_x0000____瞳_"/>
+      <sheetName val="Part_list"/>
+      <sheetName val="INACT797"/>
+      <sheetName val="M1A"/>
+      <sheetName val="OK"/>
+      <sheetName val="??? Pilling upu_S y"/>
+      <sheetName val="ASF INVENTORY"/>
+      <sheetName val="車両仕様_4___x005f_x0013__x0013__x0013__x0013__x0013_"/>
+      <sheetName val="ጀጀ؀ԀЀࠀ᐀Ѐऀ܀̀܀ഀ܀Ԁऀ଀ࠀ_x0000_"/>
+      <sheetName val="CTable"/>
+      <sheetName val="bs is"/>
+      <sheetName val="成績"/>
+      <sheetName val="IT Checklist"/>
+      <sheetName val="ﾊﾟｲﾌﾟ"/>
+      <sheetName val="冷延鋼板"/>
+      <sheetName val="熱延鋼板"/>
+      <sheetName val="他材料費"/>
+      <sheetName val="No.31"/>
+      <sheetName val="コマンド認識, DTMF"/>
+      <sheetName val="CS2_SmcDriverインテグ項目"/>
+      <sheetName val="標準仕様DB"/>
+      <sheetName val="BEEP設定"/>
+      <sheetName val="休日"/>
+      <sheetName val="工数ｺｰﾄﾞﾘｽﾄ"/>
+      <sheetName val="5．キー入力動作説明"/>
+      <sheetName val="日程"/>
+      <sheetName val="進捗"/>
+      <sheetName val="印刷"/>
+      <sheetName val="試験項目_R3小"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -14067,23 +14441,41 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="30" refreshError="1"/>
-      <sheetData sheetId="31" refreshError="1"/>
-      <sheetData sheetId="32" refreshError="1"/>
-      <sheetData sheetId="33" refreshError="1"/>
-      <sheetData sheetId="34" refreshError="1"/>
-      <sheetData sheetId="35">
+      <sheetData sheetId="30">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="31">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="32">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="33">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="34" refreshError="1"/>
+      <sheetData sheetId="35" refreshError="1"/>
       <sheetData sheetId="36" refreshError="1"/>
-      <sheetData sheetId="37"/>
-      <sheetData sheetId="38"/>
-      <sheetData sheetId="39"/>
-      <sheetData sheetId="40"/>
+      <sheetData sheetId="37" refreshError="1"/>
+      <sheetData sheetId="38" refreshError="1"/>
+      <sheetData sheetId="39" refreshError="1"/>
+      <sheetData sheetId="40" refreshError="1"/>
       <sheetData sheetId="41">
         <row r="1">
           <cell r="B1" t="str">
@@ -14105,8 +14497,20 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="44" refreshError="1"/>
-      <sheetData sheetId="45" refreshError="1"/>
+      <sheetData sheetId="44">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="45">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="46">
         <row r="1">
           <cell r="B1" t="str">
@@ -14115,29 +14519,65 @@
         </row>
       </sheetData>
       <sheetData sheetId="47" refreshError="1"/>
-      <sheetData sheetId="48"/>
+      <sheetData sheetId="48" refreshError="1"/>
       <sheetData sheetId="49" refreshError="1"/>
       <sheetData sheetId="50" refreshError="1"/>
-      <sheetData sheetId="51"/>
+      <sheetData sheetId="51" refreshError="1"/>
       <sheetData sheetId="52" refreshError="1"/>
-      <sheetData sheetId="53"/>
+      <sheetData sheetId="53" refreshError="1"/>
       <sheetData sheetId="54" refreshError="1"/>
       <sheetData sheetId="55" refreshError="1"/>
       <sheetData sheetId="56" refreshError="1"/>
       <sheetData sheetId="57" refreshError="1"/>
       <sheetData sheetId="58" refreshError="1"/>
-      <sheetData sheetId="59"/>
-      <sheetData sheetId="60"/>
-      <sheetData sheetId="61" refreshError="1"/>
-      <sheetData sheetId="62" refreshError="1"/>
-      <sheetData sheetId="63" refreshError="1"/>
-      <sheetData sheetId="64" refreshError="1"/>
+      <sheetData sheetId="59" refreshError="1"/>
+      <sheetData sheetId="60" refreshError="1"/>
+      <sheetData sheetId="61">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="62">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="63">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="64">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="65" refreshError="1"/>
       <sheetData sheetId="66" refreshError="1"/>
-      <sheetData sheetId="67"/>
-      <sheetData sheetId="68"/>
-      <sheetData sheetId="69" refreshError="1"/>
-      <sheetData sheetId="70" refreshError="1"/>
+      <sheetData sheetId="67" refreshError="1"/>
+      <sheetData sheetId="68" refreshError="1"/>
+      <sheetData sheetId="69">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="70">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="71" refreshError="1"/>
       <sheetData sheetId="72" refreshError="1"/>
       <sheetData sheetId="73" refreshError="1"/>
@@ -14227,7 +14667,7 @@
       <sheetData sheetId="157" refreshError="1"/>
       <sheetData sheetId="158" refreshError="1"/>
       <sheetData sheetId="159" refreshError="1"/>
-      <sheetData sheetId="160"/>
+      <sheetData sheetId="160" refreshError="1"/>
       <sheetData sheetId="161" refreshError="1"/>
       <sheetData sheetId="162" refreshError="1"/>
       <sheetData sheetId="163" refreshError="1"/>
@@ -14237,7 +14677,7 @@
       <sheetData sheetId="167" refreshError="1"/>
       <sheetData sheetId="168" refreshError="1"/>
       <sheetData sheetId="169" refreshError="1"/>
-      <sheetData sheetId="170" refreshError="1"/>
+      <sheetData sheetId="170"/>
       <sheetData sheetId="171" refreshError="1"/>
       <sheetData sheetId="172" refreshError="1"/>
       <sheetData sheetId="173" refreshError="1"/>
@@ -14374,33 +14814,45 @@
       <sheetData sheetId="304" refreshError="1"/>
       <sheetData sheetId="305" refreshError="1"/>
       <sheetData sheetId="306" refreshError="1"/>
-      <sheetData sheetId="307">
+      <sheetData sheetId="307" refreshError="1"/>
+      <sheetData sheetId="308" refreshError="1"/>
+      <sheetData sheetId="309" refreshError="1"/>
+      <sheetData sheetId="310" refreshError="1"/>
+      <sheetData sheetId="311">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="308">
+      <sheetData sheetId="312">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="309">
+      <sheetData sheetId="313">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="310"/>
-      <sheetData sheetId="311"/>
-      <sheetData sheetId="312" refreshError="1"/>
-      <sheetData sheetId="313" refreshError="1"/>
-      <sheetData sheetId="314" refreshError="1"/>
-      <sheetData sheetId="315" refreshError="1"/>
+      <sheetData sheetId="314">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="315">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="316" refreshError="1"/>
       <sheetData sheetId="317" refreshError="1"/>
       <sheetData sheetId="318" refreshError="1"/>
@@ -15972,8 +16424,8 @@
       </sheetData>
       <sheetData sheetId="793">
         <row r="1">
-          <cell r="B1" t="str">
-            <v>1</v>
+          <cell r="A1" t="str">
+            <v>ﾄﾖﾀ自動車株式会社　調達本部　</v>
           </cell>
         </row>
       </sheetData>
@@ -16009,7 +16461,13 @@
       <sheetData sheetId="805" refreshError="1"/>
       <sheetData sheetId="806" refreshError="1"/>
       <sheetData sheetId="807" refreshError="1"/>
-      <sheetData sheetId="808"/>
+      <sheetData sheetId="808">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="809" refreshError="1"/>
       <sheetData sheetId="810" refreshError="1"/>
       <sheetData sheetId="811" refreshError="1"/>
@@ -16972,9 +17430,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1050">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17196,9 +17654,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1082">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17217,9 +17675,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1085">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17546,9 +18004,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1132">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17637,9 +18095,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1145">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17868,16 +18326,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1178">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1179">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17917,9 +18375,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1185">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17945,9 +18403,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1189">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17966,9 +18424,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1192">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18036,9 +18494,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1202">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18057,16 +18515,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1205">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1206">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18078,16 +18536,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1208">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1209">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18127,9 +18585,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1215">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18155,9 +18613,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1219">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18176,9 +18634,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1222">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18246,9 +18704,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1232">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18267,16 +18725,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1235">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1236">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18288,16 +18746,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1238">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1239">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18337,16 +18795,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1245">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1246">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18406,16 +18864,76 @@
       <sheetData sheetId="1294"/>
       <sheetData sheetId="1295" refreshError="1"/>
       <sheetData sheetId="1296" refreshError="1"/>
-      <sheetData sheetId="1297"/>
-      <sheetData sheetId="1298"/>
-      <sheetData sheetId="1299"/>
-      <sheetData sheetId="1300"/>
-      <sheetData sheetId="1301"/>
-      <sheetData sheetId="1302"/>
-      <sheetData sheetId="1303"/>
-      <sheetData sheetId="1304"/>
-      <sheetData sheetId="1305"/>
-      <sheetData sheetId="1306"/>
+      <sheetData sheetId="1297">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1298">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1299">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1300">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1301">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1302">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1303">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1304">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1305">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1306">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1307" refreshError="1"/>
       <sheetData sheetId="1308" refreshError="1"/>
       <sheetData sheetId="1309" refreshError="1"/>
@@ -18425,13 +18943,13 @@
       <sheetData sheetId="1313" refreshError="1"/>
       <sheetData sheetId="1314" refreshError="1"/>
       <sheetData sheetId="1315" refreshError="1"/>
-      <sheetData sheetId="1316"/>
+      <sheetData sheetId="1316" refreshError="1"/>
       <sheetData sheetId="1317" refreshError="1"/>
       <sheetData sheetId="1318" refreshError="1"/>
       <sheetData sheetId="1319" refreshError="1"/>
       <sheetData sheetId="1320" refreshError="1"/>
       <sheetData sheetId="1321" refreshError="1"/>
-      <sheetData sheetId="1322" refreshError="1"/>
+      <sheetData sheetId="1322"/>
       <sheetData sheetId="1323" refreshError="1"/>
       <sheetData sheetId="1324" refreshError="1"/>
       <sheetData sheetId="1325" refreshError="1"/>
@@ -18526,39 +19044,33 @@
       <sheetData sheetId="1414" refreshError="1"/>
       <sheetData sheetId="1415" refreshError="1"/>
       <sheetData sheetId="1416" refreshError="1"/>
-      <sheetData sheetId="1417"/>
+      <sheetData sheetId="1417" refreshError="1"/>
       <sheetData sheetId="1418" refreshError="1"/>
       <sheetData sheetId="1419" refreshError="1"/>
       <sheetData sheetId="1420" refreshError="1"/>
       <sheetData sheetId="1421" refreshError="1"/>
       <sheetData sheetId="1422" refreshError="1"/>
-      <sheetData sheetId="1423"/>
-      <sheetData sheetId="1424"/>
-      <sheetData sheetId="1425"/>
-      <sheetData sheetId="1426"/>
+      <sheetData sheetId="1423" refreshError="1"/>
+      <sheetData sheetId="1424" refreshError="1"/>
+      <sheetData sheetId="1425" refreshError="1"/>
+      <sheetData sheetId="1426" refreshError="1"/>
       <sheetData sheetId="1427"/>
-      <sheetData sheetId="1428"/>
+      <sheetData sheetId="1428" refreshError="1"/>
       <sheetData sheetId="1429"/>
       <sheetData sheetId="1430"/>
       <sheetData sheetId="1431"/>
       <sheetData sheetId="1432"/>
       <sheetData sheetId="1433"/>
-      <sheetData sheetId="1434" refreshError="1"/>
-      <sheetData sheetId="1435">
-        <row r="3">
-          <cell r="C3" t="str">
-            <v>2022年</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="1434"/>
+      <sheetData sheetId="1435"/>
       <sheetData sheetId="1436"/>
       <sheetData sheetId="1437"/>
       <sheetData sheetId="1438"/>
       <sheetData sheetId="1439"/>
-      <sheetData sheetId="1440"/>
-      <sheetData sheetId="1441"/>
-      <sheetData sheetId="1442"/>
-      <sheetData sheetId="1443"/>
+      <sheetData sheetId="1440" refreshError="1"/>
+      <sheetData sheetId="1441" refreshError="1"/>
+      <sheetData sheetId="1442" refreshError="1"/>
+      <sheetData sheetId="1443" refreshError="1"/>
       <sheetData sheetId="1444"/>
       <sheetData sheetId="1445"/>
       <sheetData sheetId="1446"/>
@@ -18570,8 +19082,14 @@
       <sheetData sheetId="1452"/>
       <sheetData sheetId="1453"/>
       <sheetData sheetId="1454"/>
-      <sheetData sheetId="1455"/>
-      <sheetData sheetId="1456"/>
+      <sheetData sheetId="1455" refreshError="1"/>
+      <sheetData sheetId="1456">
+        <row r="3">
+          <cell r="C3" t="str">
+            <v>2022年</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1457"/>
       <sheetData sheetId="1458"/>
       <sheetData sheetId="1459"/>
@@ -18651,19 +19169,73 @@
       <sheetData sheetId="1533"/>
       <sheetData sheetId="1534"/>
       <sheetData sheetId="1535"/>
-      <sheetData sheetId="1536"/>
-      <sheetData sheetId="1537"/>
+      <sheetData sheetId="1536">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1537">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1538"/>
-      <sheetData sheetId="1539"/>
+      <sheetData sheetId="1539">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1540"/>
-      <sheetData sheetId="1541"/>
-      <sheetData sheetId="1542"/>
-      <sheetData sheetId="1543"/>
+      <sheetData sheetId="1541">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1542">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1543">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1544"/>
-      <sheetData sheetId="1545"/>
+      <sheetData sheetId="1545">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1546"/>
-      <sheetData sheetId="1547"/>
-      <sheetData sheetId="1548"/>
+      <sheetData sheetId="1547">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1548">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1549"/>
       <sheetData sheetId="1550"/>
       <sheetData sheetId="1551"/>
@@ -20053,52 +20625,52 @@
       <sheetData sheetId="2935"/>
       <sheetData sheetId="2936"/>
       <sheetData sheetId="2937"/>
-      <sheetData sheetId="2938">
-        <row r="1">
-          <cell r="A1"/>
-        </row>
-      </sheetData>
+      <sheetData sheetId="2938"/>
       <sheetData sheetId="2939"/>
       <sheetData sheetId="2940"/>
       <sheetData sheetId="2941"/>
-      <sheetData sheetId="2942" refreshError="1"/>
-      <sheetData sheetId="2943">
+      <sheetData sheetId="2942"/>
+      <sheetData sheetId="2943"/>
+      <sheetData sheetId="2944"/>
+      <sheetData sheetId="2945"/>
+      <sheetData sheetId="2946"/>
+      <sheetData sheetId="2947"/>
+      <sheetData sheetId="2948"/>
+      <sheetData sheetId="2949"/>
+      <sheetData sheetId="2950"/>
+      <sheetData sheetId="2951"/>
+      <sheetData sheetId="2952"/>
+      <sheetData sheetId="2953"/>
+      <sheetData sheetId="2954"/>
+      <sheetData sheetId="2955"/>
+      <sheetData sheetId="2956"/>
+      <sheetData sheetId="2957"/>
+      <sheetData sheetId="2958"/>
+      <sheetData sheetId="2959">
+        <row r="1">
+          <cell r="A1"/>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2960"/>
+      <sheetData sheetId="2961"/>
+      <sheetData sheetId="2962"/>
+      <sheetData sheetId="2963">
         <row r="1">
           <cell r="B1" t="str">
             <v>文章管理番号</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2944"/>
-      <sheetData sheetId="2945" refreshError="1"/>
-      <sheetData sheetId="2946" refreshError="1"/>
-      <sheetData sheetId="2947" refreshError="1"/>
-      <sheetData sheetId="2948" refreshError="1"/>
-      <sheetData sheetId="2949" refreshError="1"/>
-      <sheetData sheetId="2950" refreshError="1"/>
-      <sheetData sheetId="2951" refreshError="1"/>
-      <sheetData sheetId="2952" refreshError="1"/>
-      <sheetData sheetId="2953" refreshError="1"/>
-      <sheetData sheetId="2954" refreshError="1"/>
-      <sheetData sheetId="2955" refreshError="1"/>
-      <sheetData sheetId="2956" refreshError="1"/>
-      <sheetData sheetId="2957" refreshError="1"/>
-      <sheetData sheetId="2958" refreshError="1"/>
-      <sheetData sheetId="2959" refreshError="1"/>
-      <sheetData sheetId="2960" refreshError="1"/>
-      <sheetData sheetId="2961" refreshError="1"/>
-      <sheetData sheetId="2962" refreshError="1"/>
-      <sheetData sheetId="2963"/>
       <sheetData sheetId="2964"/>
-      <sheetData sheetId="2965"/>
-      <sheetData sheetId="2966"/>
-      <sheetData sheetId="2967"/>
-      <sheetData sheetId="2968"/>
-      <sheetData sheetId="2969"/>
-      <sheetData sheetId="2970"/>
-      <sheetData sheetId="2971"/>
-      <sheetData sheetId="2972"/>
-      <sheetData sheetId="2973"/>
+      <sheetData sheetId="2965" refreshError="1"/>
+      <sheetData sheetId="2966" refreshError="1"/>
+      <sheetData sheetId="2967" refreshError="1"/>
+      <sheetData sheetId="2968" refreshError="1"/>
+      <sheetData sheetId="2969" refreshError="1"/>
+      <sheetData sheetId="2970" refreshError="1"/>
+      <sheetData sheetId="2971" refreshError="1"/>
+      <sheetData sheetId="2972" refreshError="1"/>
+      <sheetData sheetId="2973" refreshError="1"/>
       <sheetData sheetId="2974" refreshError="1"/>
       <sheetData sheetId="2975"/>
       <sheetData sheetId="2976" refreshError="1"/>
@@ -20110,6 +20682,323 @@
       <sheetData sheetId="2982" refreshError="1"/>
       <sheetData sheetId="2983" refreshError="1"/>
       <sheetData sheetId="2984" refreshError="1"/>
+      <sheetData sheetId="2985" refreshError="1"/>
+      <sheetData sheetId="2986" refreshError="1"/>
+      <sheetData sheetId="2987" refreshError="1"/>
+      <sheetData sheetId="2988" refreshError="1"/>
+      <sheetData sheetId="2989" refreshError="1"/>
+      <sheetData sheetId="2990" refreshError="1"/>
+      <sheetData sheetId="2991" refreshError="1"/>
+      <sheetData sheetId="2992" refreshError="1"/>
+      <sheetData sheetId="2993" refreshError="1"/>
+      <sheetData sheetId="2994" refreshError="1"/>
+      <sheetData sheetId="2995" refreshError="1"/>
+      <sheetData sheetId="2996" refreshError="1"/>
+      <sheetData sheetId="2997" refreshError="1"/>
+      <sheetData sheetId="2998" refreshError="1"/>
+      <sheetData sheetId="2999" refreshError="1"/>
+      <sheetData sheetId="3000" refreshError="1"/>
+      <sheetData sheetId="3001" refreshError="1"/>
+      <sheetData sheetId="3002" refreshError="1"/>
+      <sheetData sheetId="3003" refreshError="1"/>
+      <sheetData sheetId="3004" refreshError="1"/>
+      <sheetData sheetId="3005" refreshError="1"/>
+      <sheetData sheetId="3006" refreshError="1"/>
+      <sheetData sheetId="3007" refreshError="1"/>
+      <sheetData sheetId="3008" refreshError="1"/>
+      <sheetData sheetId="3009" refreshError="1"/>
+      <sheetData sheetId="3010" refreshError="1"/>
+      <sheetData sheetId="3011" refreshError="1"/>
+      <sheetData sheetId="3012" refreshError="1"/>
+      <sheetData sheetId="3013" refreshError="1"/>
+      <sheetData sheetId="3014" refreshError="1"/>
+      <sheetData sheetId="3015" refreshError="1"/>
+      <sheetData sheetId="3016" refreshError="1"/>
+      <sheetData sheetId="3017" refreshError="1"/>
+      <sheetData sheetId="3018" refreshError="1"/>
+      <sheetData sheetId="3019" refreshError="1"/>
+      <sheetData sheetId="3020" refreshError="1"/>
+      <sheetData sheetId="3021" refreshError="1"/>
+      <sheetData sheetId="3022" refreshError="1"/>
+      <sheetData sheetId="3023" refreshError="1"/>
+      <sheetData sheetId="3024" refreshError="1"/>
+      <sheetData sheetId="3025" refreshError="1"/>
+      <sheetData sheetId="3026" refreshError="1"/>
+      <sheetData sheetId="3027" refreshError="1"/>
+      <sheetData sheetId="3028" refreshError="1"/>
+      <sheetData sheetId="3029" refreshError="1"/>
+      <sheetData sheetId="3030" refreshError="1"/>
+      <sheetData sheetId="3031" refreshError="1"/>
+      <sheetData sheetId="3032" refreshError="1"/>
+      <sheetData sheetId="3033" refreshError="1"/>
+      <sheetData sheetId="3034"/>
+      <sheetData sheetId="3035"/>
+      <sheetData sheetId="3036"/>
+      <sheetData sheetId="3037"/>
+      <sheetData sheetId="3038"/>
+      <sheetData sheetId="3039"/>
+      <sheetData sheetId="3040"/>
+      <sheetData sheetId="3041"/>
+      <sheetData sheetId="3042"/>
+      <sheetData sheetId="3043"/>
+      <sheetData sheetId="3044"/>
+      <sheetData sheetId="3045"/>
+      <sheetData sheetId="3046"/>
+      <sheetData sheetId="3047"/>
+      <sheetData sheetId="3048"/>
+      <sheetData sheetId="3049"/>
+      <sheetData sheetId="3050"/>
+      <sheetData sheetId="3051"/>
+      <sheetData sheetId="3052"/>
+      <sheetData sheetId="3053"/>
+      <sheetData sheetId="3054"/>
+      <sheetData sheetId="3055"/>
+      <sheetData sheetId="3056"/>
+      <sheetData sheetId="3057"/>
+      <sheetData sheetId="3058"/>
+      <sheetData sheetId="3059"/>
+      <sheetData sheetId="3060"/>
+      <sheetData sheetId="3061"/>
+      <sheetData sheetId="3062"/>
+      <sheetData sheetId="3063"/>
+      <sheetData sheetId="3064"/>
+      <sheetData sheetId="3065"/>
+      <sheetData sheetId="3066"/>
+      <sheetData sheetId="3067"/>
+      <sheetData sheetId="3068"/>
+      <sheetData sheetId="3069"/>
+      <sheetData sheetId="3070"/>
+      <sheetData sheetId="3071"/>
+      <sheetData sheetId="3072"/>
+      <sheetData sheetId="3073"/>
+      <sheetData sheetId="3074"/>
+      <sheetData sheetId="3075"/>
+      <sheetData sheetId="3076"/>
+      <sheetData sheetId="3077">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3078">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3079">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3080">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3081">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3082">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3083">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3084">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3085">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3086">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3087">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3088">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3089">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3090">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3091">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3092">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3093">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3094">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3095">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3096">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3097">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3098">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3099">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3100"/>
+      <sheetData sheetId="3101"/>
+      <sheetData sheetId="3102"/>
+      <sheetData sheetId="3103"/>
+      <sheetData sheetId="3104"/>
+      <sheetData sheetId="3105"/>
+      <sheetData sheetId="3106"/>
+      <sheetData sheetId="3107"/>
+      <sheetData sheetId="3108"/>
+      <sheetData sheetId="3109"/>
+      <sheetData sheetId="3110"/>
+      <sheetData sheetId="3111"/>
+      <sheetData sheetId="3112"/>
+      <sheetData sheetId="3113"/>
+      <sheetData sheetId="3114"/>
+      <sheetData sheetId="3115"/>
+      <sheetData sheetId="3116"/>
+      <sheetData sheetId="3117"/>
+      <sheetData sheetId="3118"/>
+      <sheetData sheetId="3119"/>
+      <sheetData sheetId="3120"/>
+      <sheetData sheetId="3121"/>
+      <sheetData sheetId="3122"/>
+      <sheetData sheetId="3123"/>
+      <sheetData sheetId="3124"/>
+      <sheetData sheetId="3125"/>
+      <sheetData sheetId="3126"/>
+      <sheetData sheetId="3127"/>
+      <sheetData sheetId="3128"/>
+      <sheetData sheetId="3129"/>
+      <sheetData sheetId="3130"/>
+      <sheetData sheetId="3131"/>
+      <sheetData sheetId="3132"/>
+      <sheetData sheetId="3133"/>
+      <sheetData sheetId="3134"/>
+      <sheetData sheetId="3135"/>
+      <sheetData sheetId="3136"/>
+      <sheetData sheetId="3137" refreshError="1"/>
+      <sheetData sheetId="3138" refreshError="1"/>
+      <sheetData sheetId="3139" refreshError="1"/>
+      <sheetData sheetId="3140" refreshError="1"/>
+      <sheetData sheetId="3141" refreshError="1"/>
+      <sheetData sheetId="3142" refreshError="1"/>
+      <sheetData sheetId="3143" refreshError="1"/>
+      <sheetData sheetId="3144" refreshError="1"/>
+      <sheetData sheetId="3145" refreshError="1"/>
+      <sheetData sheetId="3146" refreshError="1"/>
+      <sheetData sheetId="3147" refreshError="1"/>
+      <sheetData sheetId="3148" refreshError="1"/>
+      <sheetData sheetId="3149" refreshError="1"/>
+      <sheetData sheetId="3150" refreshError="1"/>
+      <sheetData sheetId="3151" refreshError="1"/>
+      <sheetData sheetId="3152" refreshError="1"/>
+      <sheetData sheetId="3153" refreshError="1"/>
+      <sheetData sheetId="3154" refreshError="1"/>
+      <sheetData sheetId="3155" refreshError="1"/>
+      <sheetData sheetId="3156" refreshError="1"/>
+      <sheetData sheetId="3157" refreshError="1"/>
+      <sheetData sheetId="3158" refreshError="1"/>
+      <sheetData sheetId="3159" refreshError="1"/>
+      <sheetData sheetId="3160" refreshError="1"/>
+      <sheetData sheetId="3161" refreshError="1"/>
+      <sheetData sheetId="3162" refreshError="1"/>
+      <sheetData sheetId="3163" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -20204,17 +21093,62 @@
       <sheetName val="_UnderConst_Analysis"/>
       <sheetName val="アップロード系(2)"/>
       <sheetName val="List"/>
+      <sheetName val="パラメータ設定表"/>
       <sheetName val="別紙7_操作系イベント発生時_"/>
       <sheetName val="別紙11_各競合条件における起動可否_"/>
       <sheetName val="index"/>
-      <sheetName val="パラメータ設定表"/>
+      <sheetName val="入力"/>
+      <sheetName val="415T戟L"/>
+      <sheetName val="No.31"/>
       <sheetName val="改訂履歴"/>
       <sheetName val="リスト"/>
       <sheetName val="ドメイン"/>
       <sheetName val="format"/>
-      <sheetName val="入力"/>
-      <sheetName val="415T戟L"/>
-      <sheetName val="No.31"/>
+      <sheetName val="Navigation"/>
+      <sheetName val="Cover"/>
+      <sheetName val="DataList"/>
+      <sheetName val="変更要件"/>
+      <sheetName val="【石倉編集中】DisplayStateTransitionTa"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="R0-10表紙"/>
+      <sheetName val="Calcul"/>
+      <sheetName val="Data"/>
+      <sheetName val="★VarUsed"/>
+      <sheetName val="輝度計算(直線用)"/>
+      <sheetName val="コード_dimautocon"/>
+      <sheetName val="パラメータ_dimautocon"/>
+      <sheetName val="パラメータ_dimcalprcnt"/>
+      <sheetName val="パラメータ_dimmanualstep"/>
+      <sheetName val="パラメータ_dimmgr"/>
+      <sheetName val="XX-0080"/>
+      <sheetName val="メッセージ定義"/>
+      <sheetName val="XX-0180"/>
+      <sheetName val="lock"/>
+      <sheetName val="level"/>
+      <sheetName val="cominf"/>
+      <sheetName val="disconnect"/>
+      <sheetName val="９ｘ"/>
+      <sheetName val="Ｂｘ"/>
+      <sheetName val="Ｃｘ"/>
+      <sheetName val="Ｅｘ"/>
+      <sheetName val="休日"/>
+      <sheetName val="HMI-004_Screen（old）"/>
+      <sheetName val="ﾊﾟｲﾌﾟ"/>
+      <sheetName val="冷延鋼板"/>
+      <sheetName val="熱延鋼板"/>
+      <sheetName val="他材料費"/>
+      <sheetName val="MOTO"/>
+      <sheetName val="前提書情報"/>
+      <sheetName val="②P071中計　工数パターン1312更新"/>
+      <sheetName val="module"/>
+      <sheetName val="選択肢"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="メニュー"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="R0-10表紙MIC"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="修正ﾌｧｲﾙ一覧"/>
+      <sheetName val="RGB"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -20313,6 +21247,51 @@
       <sheetData sheetId="93" refreshError="1"/>
       <sheetData sheetId="94" refreshError="1"/>
       <sheetData sheetId="95" refreshError="1"/>
+      <sheetData sheetId="96" refreshError="1"/>
+      <sheetData sheetId="97" refreshError="1"/>
+      <sheetData sheetId="98" refreshError="1"/>
+      <sheetData sheetId="99" refreshError="1"/>
+      <sheetData sheetId="100" refreshError="1"/>
+      <sheetData sheetId="101" refreshError="1"/>
+      <sheetData sheetId="102" refreshError="1"/>
+      <sheetData sheetId="103" refreshError="1"/>
+      <sheetData sheetId="104" refreshError="1"/>
+      <sheetData sheetId="105" refreshError="1"/>
+      <sheetData sheetId="106" refreshError="1"/>
+      <sheetData sheetId="107" refreshError="1"/>
+      <sheetData sheetId="108" refreshError="1"/>
+      <sheetData sheetId="109" refreshError="1"/>
+      <sheetData sheetId="110" refreshError="1"/>
+      <sheetData sheetId="111" refreshError="1"/>
+      <sheetData sheetId="112" refreshError="1"/>
+      <sheetData sheetId="113" refreshError="1"/>
+      <sheetData sheetId="114" refreshError="1"/>
+      <sheetData sheetId="115" refreshError="1"/>
+      <sheetData sheetId="116" refreshError="1"/>
+      <sheetData sheetId="117" refreshError="1"/>
+      <sheetData sheetId="118" refreshError="1"/>
+      <sheetData sheetId="119" refreshError="1"/>
+      <sheetData sheetId="120" refreshError="1"/>
+      <sheetData sheetId="121" refreshError="1"/>
+      <sheetData sheetId="122" refreshError="1"/>
+      <sheetData sheetId="123" refreshError="1"/>
+      <sheetData sheetId="124" refreshError="1"/>
+      <sheetData sheetId="125" refreshError="1"/>
+      <sheetData sheetId="126" refreshError="1"/>
+      <sheetData sheetId="127" refreshError="1"/>
+      <sheetData sheetId="128" refreshError="1"/>
+      <sheetData sheetId="129" refreshError="1"/>
+      <sheetData sheetId="130" refreshError="1"/>
+      <sheetData sheetId="131" refreshError="1"/>
+      <sheetData sheetId="132" refreshError="1"/>
+      <sheetData sheetId="133" refreshError="1"/>
+      <sheetData sheetId="134" refreshError="1"/>
+      <sheetData sheetId="135" refreshError="1"/>
+      <sheetData sheetId="136" refreshError="1"/>
+      <sheetData sheetId="137" refreshError="1"/>
+      <sheetData sheetId="138" refreshError="1"/>
+      <sheetData sheetId="139" refreshError="1"/>
+      <sheetData sheetId="140" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -20609,10 +21588,10 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="C1:AM57"/>
-  <sheetFormatPr defaultColWidth="8.125" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="8.08984375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="52" width="2.125" style="224" customWidth="1"/>
-    <col min="53" max="16384" width="8.125" style="224"/>
+    <col min="1" max="52" width="2.08984375" style="224" customWidth="1"/>
+    <col min="53" max="16384" width="8.08984375" style="224"/>
   </cols>
   <sheetData>
     <row r="1" spans="6:20" ht="13.15" customHeight="1"/>
@@ -20671,31 +21650,31 @@
     </row>
     <row r="34" spans="3:39" ht="13.15" customHeight="1">
       <c r="Y34" s="227" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y35" s="244" t="s">
-        <v>283</v>
-      </c>
-      <c r="Z35" s="245"/>
-      <c r="AA35" s="245"/>
-      <c r="AB35" s="245"/>
-      <c r="AC35" s="246"/>
-      <c r="AD35" s="244" t="s">
-        <v>284</v>
-      </c>
-      <c r="AE35" s="245"/>
-      <c r="AF35" s="245"/>
-      <c r="AG35" s="245"/>
-      <c r="AH35" s="246"/>
-      <c r="AI35" s="244" t="s">
-        <v>285</v>
-      </c>
-      <c r="AJ35" s="245"/>
-      <c r="AK35" s="245"/>
-      <c r="AL35" s="245"/>
-      <c r="AM35" s="246"/>
+      <c r="Y35" s="249" t="s">
+        <v>280</v>
+      </c>
+      <c r="Z35" s="250"/>
+      <c r="AA35" s="250"/>
+      <c r="AB35" s="250"/>
+      <c r="AC35" s="251"/>
+      <c r="AD35" s="249" t="s">
+        <v>281</v>
+      </c>
+      <c r="AE35" s="250"/>
+      <c r="AF35" s="250"/>
+      <c r="AG35" s="250"/>
+      <c r="AH35" s="251"/>
+      <c r="AI35" s="249" t="s">
+        <v>282</v>
+      </c>
+      <c r="AJ35" s="250"/>
+      <c r="AK35" s="250"/>
+      <c r="AL35" s="250"/>
+      <c r="AM35" s="251"/>
     </row>
     <row r="36" spans="3:39" ht="13.15" customHeight="1">
       <c r="D36" s="228"/>
@@ -20741,21 +21720,21 @@
       <c r="Y38" s="233"/>
       <c r="Z38" s="228"/>
       <c r="AA38" s="229" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AB38" s="228"/>
       <c r="AC38" s="235"/>
       <c r="AD38" s="233"/>
       <c r="AE38" s="228"/>
       <c r="AF38" s="229" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AG38" s="228"/>
       <c r="AH38" s="235"/>
       <c r="AI38" s="236"/>
       <c r="AJ38" s="228"/>
       <c r="AK38" s="229" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AL38" s="228"/>
       <c r="AM38" s="235"/>
@@ -20790,31 +21769,31 @@
     <row r="41" spans="3:39" ht="13.15" customHeight="1"/>
     <row r="42" spans="3:39" ht="13.15" customHeight="1">
       <c r="Y42" s="227" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="43" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y43" s="244" t="s">
-        <v>283</v>
-      </c>
-      <c r="Z43" s="245"/>
-      <c r="AA43" s="245"/>
-      <c r="AB43" s="245"/>
-      <c r="AC43" s="246"/>
-      <c r="AD43" s="244" t="s">
-        <v>284</v>
-      </c>
-      <c r="AE43" s="245"/>
-      <c r="AF43" s="245"/>
-      <c r="AG43" s="245"/>
-      <c r="AH43" s="246"/>
-      <c r="AI43" s="244" t="s">
-        <v>285</v>
-      </c>
-      <c r="AJ43" s="245"/>
-      <c r="AK43" s="245"/>
-      <c r="AL43" s="245"/>
-      <c r="AM43" s="246"/>
+      <c r="Y43" s="249" t="s">
+        <v>280</v>
+      </c>
+      <c r="Z43" s="250"/>
+      <c r="AA43" s="250"/>
+      <c r="AB43" s="250"/>
+      <c r="AC43" s="251"/>
+      <c r="AD43" s="249" t="s">
+        <v>281</v>
+      </c>
+      <c r="AE43" s="250"/>
+      <c r="AF43" s="250"/>
+      <c r="AG43" s="250"/>
+      <c r="AH43" s="251"/>
+      <c r="AI43" s="249" t="s">
+        <v>282</v>
+      </c>
+      <c r="AJ43" s="250"/>
+      <c r="AK43" s="250"/>
+      <c r="AL43" s="250"/>
+      <c r="AM43" s="251"/>
     </row>
     <row r="44" spans="3:39" ht="13.15" customHeight="1">
       <c r="D44" s="228"/>
@@ -20860,21 +21839,21 @@
       <c r="Y46" s="233"/>
       <c r="Z46" s="228"/>
       <c r="AA46" s="229" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="AB46" s="228"/>
       <c r="AC46" s="235"/>
       <c r="AD46" s="228"/>
       <c r="AE46" s="228"/>
       <c r="AF46" s="229" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="AG46" s="228"/>
       <c r="AH46" s="235"/>
       <c r="AI46" s="236"/>
       <c r="AJ46" s="228"/>
       <c r="AK46" s="229" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="AL46" s="228"/>
       <c r="AM46" s="235"/>
@@ -20908,31 +21887,31 @@
     <row r="49" spans="4:39" ht="13.15" customHeight="1"/>
     <row r="50" spans="4:39" ht="13.15" customHeight="1">
       <c r="Y50" s="227" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="51" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y51" s="244" t="s">
-        <v>283</v>
-      </c>
-      <c r="Z51" s="245"/>
-      <c r="AA51" s="245"/>
-      <c r="AB51" s="245"/>
-      <c r="AC51" s="246"/>
-      <c r="AD51" s="244" t="s">
-        <v>284</v>
-      </c>
-      <c r="AE51" s="245"/>
-      <c r="AF51" s="245"/>
-      <c r="AG51" s="245"/>
-      <c r="AH51" s="246"/>
-      <c r="AI51" s="244" t="s">
-        <v>285</v>
-      </c>
-      <c r="AJ51" s="245"/>
-      <c r="AK51" s="245"/>
-      <c r="AL51" s="245"/>
-      <c r="AM51" s="246"/>
+      <c r="Y51" s="249" t="s">
+        <v>280</v>
+      </c>
+      <c r="Z51" s="250"/>
+      <c r="AA51" s="250"/>
+      <c r="AB51" s="250"/>
+      <c r="AC51" s="251"/>
+      <c r="AD51" s="249" t="s">
+        <v>281</v>
+      </c>
+      <c r="AE51" s="250"/>
+      <c r="AF51" s="250"/>
+      <c r="AG51" s="250"/>
+      <c r="AH51" s="251"/>
+      <c r="AI51" s="249" t="s">
+        <v>282</v>
+      </c>
+      <c r="AJ51" s="250"/>
+      <c r="AK51" s="250"/>
+      <c r="AL51" s="250"/>
+      <c r="AM51" s="251"/>
     </row>
     <row r="52" spans="4:39" ht="13.15" customHeight="1">
       <c r="D52" s="228"/>
@@ -20978,21 +21957,21 @@
       <c r="Y54" s="233"/>
       <c r="Z54" s="228"/>
       <c r="AA54" s="229" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AB54" s="228"/>
       <c r="AC54" s="235"/>
       <c r="AD54" s="228"/>
       <c r="AE54" s="228"/>
       <c r="AF54" s="229" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AG54" s="228"/>
       <c r="AH54" s="235"/>
       <c r="AI54" s="236"/>
       <c r="AJ54" s="228"/>
       <c r="AK54" s="229" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AL54" s="228"/>
       <c r="AM54" s="235"/>
@@ -21023,7 +22002,7 @@
     </row>
     <row r="57" spans="4:39" ht="13.15" customHeight="1">
       <c r="AK57" s="224" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -21052,14 +22031,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:X13"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="4.5" customWidth="1"/>
+    <col min="1" max="1" width="4.453125" customWidth="1"/>
     <col min="2" max="2" width="9" style="9" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="69.5" customWidth="1"/>
-    <col min="5" max="6" width="12.75" customWidth="1"/>
-    <col min="7" max="22" width="13.125" hidden="1" customWidth="1"/>
-    <col min="23" max="24" width="13.125" customWidth="1"/>
+    <col min="4" max="4" width="69.453125" customWidth="1"/>
+    <col min="5" max="6" width="12.7265625" customWidth="1"/>
+    <col min="7" max="22" width="13.08984375" hidden="1" customWidth="1"/>
+    <col min="23" max="24" width="13.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="25.5" customHeight="1">
@@ -21070,18 +22049,18 @@
       <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="255" t="s">
+      <c r="I2" s="252" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="255"/>
-      <c r="K2" s="255"/>
-      <c r="L2" s="255"/>
-      <c r="M2" s="255"/>
-      <c r="N2" s="255"/>
-      <c r="O2" s="255"/>
-      <c r="P2" s="255"/>
-      <c r="Q2" s="255"/>
-      <c r="R2" s="255"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
+      <c r="M2" s="252"/>
+      <c r="N2" s="252"/>
+      <c r="O2" s="252"/>
+      <c r="P2" s="252"/>
+      <c r="Q2" s="252"/>
+      <c r="R2" s="252"/>
     </row>
     <row r="3" spans="2:24" ht="25.5" customHeight="1">
       <c r="C3" s="6"/>
@@ -21094,25 +22073,25 @@
       <c r="H3" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="I3" s="256" t="s">
+      <c r="I3" s="253" t="s">
         <v>218</v>
       </c>
-      <c r="J3" s="257"/>
-      <c r="K3" s="257"/>
-      <c r="L3" s="257"/>
-      <c r="M3" s="257"/>
-      <c r="N3" s="257"/>
-      <c r="O3" s="257"/>
-      <c r="P3" s="257"/>
-      <c r="Q3" s="257"/>
-      <c r="R3" s="257"/>
+      <c r="J3" s="254"/>
+      <c r="K3" s="254"/>
+      <c r="L3" s="254"/>
+      <c r="M3" s="254"/>
+      <c r="N3" s="254"/>
+      <c r="O3" s="254"/>
+      <c r="P3" s="254"/>
+      <c r="Q3" s="254"/>
+      <c r="R3" s="254"/>
     </row>
     <row r="4" spans="2:24" ht="25.5" customHeight="1">
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="22" t="str">
         <f>DGET(B8:C14,"Ver.",H4:H5)</f>
-        <v>1.1.2</v>
+        <v>1.1.3</v>
       </c>
       <c r="F4" s="6"/>
       <c r="H4" s="9" t="s">
@@ -21126,45 +22105,45 @@
       <c r="F5" s="6"/>
       <c r="H5" s="11">
         <f>MAX(B9:B14)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:24" ht="14.25" thickBot="1"/>
+    <row r="6" spans="2:24" ht="13.5" thickBot="1"/>
     <row r="7" spans="2:24">
-      <c r="C7" s="249" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="250"/>
-      <c r="E7" s="251" t="s">
+      <c r="C7" s="257" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="258"/>
+      <c r="E7" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="251"/>
-      <c r="G7" s="252" t="s">
+      <c r="F7" s="259"/>
+      <c r="G7" s="260" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="252"/>
-      <c r="I7" s="252"/>
-      <c r="J7" s="252"/>
-      <c r="K7" s="252"/>
-      <c r="L7" s="252"/>
-      <c r="M7" s="253" t="s">
+      <c r="H7" s="260"/>
+      <c r="I7" s="260"/>
+      <c r="J7" s="260"/>
+      <c r="K7" s="260"/>
+      <c r="L7" s="260"/>
+      <c r="M7" s="261" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="253"/>
-      <c r="O7" s="253"/>
-      <c r="P7" s="253"/>
-      <c r="Q7" s="253"/>
-      <c r="R7" s="254"/>
-      <c r="S7" s="247" t="s">
-        <v>297</v>
-      </c>
-      <c r="T7" s="247"/>
-      <c r="U7" s="247"/>
-      <c r="V7" s="247"/>
-      <c r="W7" s="247"/>
-      <c r="X7" s="248"/>
+      <c r="N7" s="261"/>
+      <c r="O7" s="261"/>
+      <c r="P7" s="261"/>
+      <c r="Q7" s="261"/>
+      <c r="R7" s="262"/>
+      <c r="S7" s="255" t="s">
+        <v>294</v>
+      </c>
+      <c r="T7" s="255"/>
+      <c r="U7" s="255"/>
+      <c r="V7" s="255"/>
+      <c r="W7" s="255"/>
+      <c r="X7" s="256"/>
     </row>
-    <row r="8" spans="2:24" ht="27.75" thickBot="1">
+    <row r="8" spans="2:24" ht="26.5" thickBot="1">
       <c r="B8" s="9" t="s">
         <v>15</v>
       </c>
@@ -21217,7 +22196,7 @@
         <v>11</v>
       </c>
       <c r="S8" s="16" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="T8" s="16" t="s">
         <v>7</v>
@@ -21235,22 +22214,22 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:24" ht="108.75" thickTop="1">
+    <row r="9" spans="2:24" ht="104.5" thickTop="1">
       <c r="B9" s="9">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D9" s="220" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>31</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>31</v>
@@ -21275,7 +22254,7 @@
       <c r="O9" s="13"/>
       <c r="P9" s="13"/>
       <c r="Q9" s="13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="R9" s="219">
         <v>44277</v>
@@ -21299,29 +22278,29 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="2:24" ht="135">
+    <row r="10" spans="2:24" ht="130">
       <c r="B10" s="9">
         <f t="shared" ref="B10:B13" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D10" s="243" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L10" s="1">
         <v>45322</v>
@@ -21363,16 +22342,16 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="2:24" ht="40.5">
+    <row r="11" spans="2:24" ht="39">
       <c r="B11" s="9">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D11" s="243" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>31</v>
@@ -21409,21 +22388,29 @@
       <c r="U11" s="1"/>
       <c r="V11" s="219"/>
       <c r="W11" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="X11" s="218">
         <v>45806</v>
       </c>
     </row>
-    <row r="12" spans="2:24">
+    <row r="12" spans="2:24" ht="91">
       <c r="B12" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="C12" s="244" t="s">
+        <v>303</v>
+      </c>
+      <c r="D12" s="245" t="s">
+        <v>306</v>
+      </c>
+      <c r="E12" s="246" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="246" t="s">
+        <v>31</v>
+      </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -21440,10 +22427,14 @@
       <c r="T12" s="219"/>
       <c r="U12" s="1"/>
       <c r="V12" s="219"/>
-      <c r="W12" s="1"/>
-      <c r="X12" s="218"/>
+      <c r="W12" s="247" t="s">
+        <v>302</v>
+      </c>
+      <c r="X12" s="248">
+        <v>46008</v>
+      </c>
     </row>
-    <row r="13" spans="2:24" ht="14.25" thickBot="1">
+    <row r="13" spans="2:24" ht="13.5" thickBot="1">
       <c r="B13" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -21497,11 +22488,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="4.625" customWidth="1"/>
-    <col min="3" max="3" width="3.5" customWidth="1"/>
-    <col min="4" max="4" width="17.5" customWidth="1"/>
+    <col min="2" max="2" width="4.6328125" customWidth="1"/>
+    <col min="3" max="3" width="3.453125" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -21515,13 +22506,13 @@
         <v>143</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="14.25" thickBot="1">
+    <row r="6" spans="2:5" ht="13.5" thickBot="1">
       <c r="B6" s="159" t="s">
         <v>134</v>
       </c>
       <c r="C6" s="159"/>
     </row>
-    <row r="7" spans="2:5" ht="14.25" thickBot="1">
+    <row r="7" spans="2:5" ht="13.5" thickBot="1">
       <c r="C7" s="84" t="s">
         <v>136</v>
       </c>
@@ -21541,7 +22532,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="27">
+    <row r="9" spans="2:5" ht="26">
       <c r="C9" s="169">
         <v>1</v>
       </c>
@@ -21552,7 +22543,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="14.25" thickBot="1">
+    <row r="10" spans="2:5" ht="13.5" thickBot="1">
       <c r="C10" s="167"/>
       <c r="D10" s="95"/>
       <c r="E10" s="5"/>
@@ -21560,14 +22551,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="165"/>
     </row>
-    <row r="12" spans="2:5" ht="14.25" thickBot="1">
+    <row r="12" spans="2:5" ht="13.5" thickBot="1">
       <c r="B12" s="160" t="s">
         <v>135</v>
       </c>
       <c r="C12" s="91"/>
       <c r="D12" s="91"/>
     </row>
-    <row r="13" spans="2:5" ht="14.25" thickBot="1">
+    <row r="13" spans="2:5" ht="13.5" thickBot="1">
       <c r="B13" s="161"/>
       <c r="C13" s="166" t="s">
         <v>136</v>
@@ -21579,7 +22570,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="14.25" thickTop="1">
+    <row r="14" spans="2:5" ht="13.5" thickTop="1">
       <c r="C14" s="163">
         <v>0</v>
       </c>
@@ -21656,17 +22647,17 @@
         <v>186</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="14.25" thickBot="1">
+    <row r="21" spans="2:5" ht="13.5" thickBot="1">
       <c r="C21" s="167"/>
       <c r="D21" s="95"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="24" spans="2:5" ht="14.25" thickBot="1">
+    <row r="24" spans="2:5" ht="13.5" thickBot="1">
       <c r="B24" s="159" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="14.25" thickBot="1">
+    <row r="25" spans="2:5" ht="13.5" thickBot="1">
       <c r="C25" s="166" t="s">
         <v>136</v>
       </c>
@@ -21753,26 +22744,26 @@
       <c r="D33" s="94"/>
       <c r="E33" s="80"/>
     </row>
-    <row r="34" spans="2:5" ht="14.25" thickBot="1">
+    <row r="34" spans="2:5" ht="13.5" thickBot="1">
       <c r="C34" s="167"/>
       <c r="D34" s="95"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="37" spans="2:5" ht="14.25" thickBot="1">
+    <row r="37" spans="2:5" ht="13.5" thickBot="1">
       <c r="B37" s="159" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="38" spans="2:5">
-      <c r="C38" s="258"/>
-      <c r="D38" s="259"/>
+      <c r="C38" s="263"/>
+      <c r="D38" s="264"/>
       <c r="E38" s="120" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="14.25" thickBot="1">
-      <c r="C39" s="260"/>
-      <c r="D39" s="261"/>
+    <row r="39" spans="2:5" ht="13.5" thickBot="1">
+      <c r="C39" s="265"/>
+      <c r="D39" s="266"/>
       <c r="E39" s="5" t="s">
         <v>122</v>
       </c>
@@ -21801,131 +22792,131 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.75" customWidth="1"/>
-    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.7265625" customWidth="1"/>
+    <col min="9" max="9" width="20.90625" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
+    <row r="1" spans="2:14" ht="13.5" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="287" t="s">
+      <c r="B2" s="292" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="288"/>
-      <c r="D2" s="275" t="s">
-        <v>278</v>
-      </c>
-      <c r="E2" s="276"/>
-      <c r="F2" s="276"/>
-      <c r="G2" s="276"/>
-      <c r="H2" s="277"/>
+      <c r="C2" s="293"/>
+      <c r="D2" s="280" t="s">
+        <v>276</v>
+      </c>
+      <c r="E2" s="281"/>
+      <c r="F2" s="281"/>
+      <c r="G2" s="281"/>
+      <c r="H2" s="282"/>
     </row>
     <row r="3" spans="2:14" ht="13.15" customHeight="1">
-      <c r="B3" s="262" t="s">
+      <c r="B3" s="267" t="s">
         <v>119</v>
       </c>
-      <c r="C3" s="263"/>
-      <c r="D3" s="278" t="s">
-        <v>279</v>
-      </c>
-      <c r="E3" s="279"/>
-      <c r="F3" s="279"/>
-      <c r="G3" s="279"/>
-      <c r="H3" s="280"/>
+      <c r="C3" s="268"/>
+      <c r="D3" s="283" t="s">
+        <v>277</v>
+      </c>
+      <c r="E3" s="284"/>
+      <c r="F3" s="284"/>
+      <c r="G3" s="284"/>
+      <c r="H3" s="285"/>
     </row>
-    <row r="4" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B4" s="273" t="s">
+    <row r="4" spans="2:14" ht="13.5" thickBot="1">
+      <c r="B4" s="278" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="274"/>
-      <c r="D4" s="281" t="str">
+      <c r="C4" s="279"/>
+      <c r="D4" s="286" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_B_LEDHEA-CSTD-1-00-A-C0.c</v>
       </c>
-      <c r="E4" s="282"/>
-      <c r="F4" s="282"/>
-      <c r="G4" s="282"/>
-      <c r="H4" s="283"/>
+      <c r="E4" s="287"/>
+      <c r="F4" s="287"/>
+      <c r="G4" s="287"/>
+      <c r="H4" s="288"/>
     </row>
-    <row r="5" spans="2:14" ht="14.25" thickBot="1">
+    <row r="5" spans="2:14" ht="13.5" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="287" t="s">
+      <c r="B6" s="292" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="288"/>
-      <c r="D6" s="284" t="str">
+      <c r="C6" s="293"/>
+      <c r="D6" s="289" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>B_LEDHEA</v>
       </c>
-      <c r="E6" s="285"/>
-      <c r="F6" s="285"/>
-      <c r="G6" s="285"/>
-      <c r="H6" s="286"/>
+      <c r="E6" s="290"/>
+      <c r="F6" s="290"/>
+      <c r="G6" s="290"/>
+      <c r="H6" s="291"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="262" t="s">
+      <c r="B7" s="267" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="263"/>
-      <c r="D7" s="264">
+      <c r="C7" s="268"/>
+      <c r="D7" s="269">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="265"/>
-      <c r="F7" s="265"/>
-      <c r="G7" s="265"/>
-      <c r="H7" s="266"/>
+      <c r="E7" s="270"/>
+      <c r="F7" s="270"/>
+      <c r="G7" s="270"/>
+      <c r="H7" s="271"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="262" t="s">
+      <c r="B8" s="267" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="263"/>
-      <c r="D8" s="264" t="str">
+      <c r="C8" s="268"/>
+      <c r="D8" s="269" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_B_LEDHEA_MTRX</v>
       </c>
-      <c r="E8" s="265"/>
-      <c r="F8" s="265"/>
-      <c r="G8" s="265"/>
-      <c r="H8" s="266"/>
+      <c r="E8" s="270"/>
+      <c r="F8" s="270"/>
+      <c r="G8" s="270"/>
+      <c r="H8" s="271"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="262" t="s">
+      <c r="B9" s="267" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="263"/>
-      <c r="D9" s="267" t="s">
+      <c r="C9" s="268"/>
+      <c r="D9" s="272" t="s">
         <v>225</v>
       </c>
-      <c r="E9" s="268"/>
-      <c r="F9" s="268"/>
-      <c r="G9" s="268"/>
-      <c r="H9" s="269"/>
+      <c r="E9" s="273"/>
+      <c r="F9" s="273"/>
+      <c r="G9" s="273"/>
+      <c r="H9" s="274"/>
     </row>
-    <row r="10" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B10" s="273" t="s">
+    <row r="10" spans="2:14" ht="13.5" thickBot="1">
+      <c r="B10" s="278" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="274"/>
-      <c r="D10" s="270"/>
-      <c r="E10" s="271"/>
-      <c r="F10" s="271"/>
-      <c r="G10" s="271"/>
-      <c r="H10" s="272"/>
+      <c r="C10" s="279"/>
+      <c r="D10" s="275"/>
+      <c r="E10" s="276"/>
+      <c r="F10" s="276"/>
+      <c r="G10" s="276"/>
+      <c r="H10" s="277"/>
     </row>
-    <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
-    <row r="12" spans="2:14" ht="14.25" thickBot="1">
+    <row r="11" spans="2:14" ht="13.5" thickBot="1"/>
+    <row r="12" spans="2:14" ht="13.5" thickBot="1">
       <c r="B12" s="150" t="s">
         <v>38</v>
       </c>
@@ -21960,7 +22951,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="14.25" thickTop="1">
+    <row r="13" spans="2:14" ht="13.5" thickTop="1">
       <c r="B13" s="113">
         <v>1</v>
       </c>
@@ -21971,15 +22962,15 @@
         <v>52</v>
       </c>
       <c r="E13" s="119" t="s">
-        <v>235</v>
+        <v>304</v>
       </c>
       <c r="F13" s="56" t="str">
         <f t="shared" ref="F13:F37" ca="1" si="0">IF($D13&lt;&gt;"","u4_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"Srcchk","")</f>
         <v>u4_s_AlertB_ledheaSrcchk</v>
       </c>
       <c r="G13" s="56" t="str">
-        <f t="shared" ref="G13:G37" ca="1" si="1">IF($D13&lt;&gt;"",IF($E13="○","vd_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"RwTx","NULL"),"")</f>
-        <v>vd_s_AlertB_ledheaRwTx</v>
+        <f t="shared" ref="G13:G37" si="1">IF($D13&lt;&gt;"",IF($E13="○","vd_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"RwTx","NULL"),"")</f>
+        <v>NULL</v>
       </c>
       <c r="H13" s="117" t="str">
         <f ca="1">IF($D13&lt;&gt;"","ALERT_CH_"&amp;UPPER($D$6)&amp;IF($D$7=1,"","_"&amp;UPPER($C13)),"")</f>
@@ -22813,7 +23804,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="14.25" thickBot="1">
+    <row r="37" spans="2:14" ht="13.5" thickBot="1">
       <c r="B37" s="104">
         <v>25</v>
       </c>
@@ -22915,21 +23906,21 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.5" customWidth="1"/>
-    <col min="6" max="6" width="52.75" customWidth="1"/>
-    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.875" customWidth="1"/>
-    <col min="16" max="16" width="9.875" customWidth="1"/>
-    <col min="17" max="17" width="44.625" customWidth="1"/>
-    <col min="18" max="18" width="73.625" customWidth="1"/>
+    <col min="5" max="5" width="36.453125" customWidth="1"/>
+    <col min="6" max="6" width="52.7265625" customWidth="1"/>
+    <col min="7" max="7" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.90625" customWidth="1"/>
+    <col min="16" max="16" width="9.90625" customWidth="1"/>
+    <col min="17" max="17" width="44.6328125" customWidth="1"/>
+    <col min="18" max="18" width="73.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="14.25" thickBot="1">
+    <row r="2" spans="2:18" ht="13.5" thickBot="1">
       <c r="B2" t="s">
         <v>208</v>
       </c>
@@ -22937,7 +23928,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="14.25" thickBot="1">
+    <row r="3" spans="2:18" ht="13.5" thickBot="1">
       <c r="B3" s="150" t="s">
         <v>38</v>
       </c>
@@ -22975,7 +23966,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="14.25" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="13.5" hidden="1" thickTop="1">
       <c r="B4" s="181">
         <v>0</v>
       </c>
@@ -23003,7 +23994,7 @@
       </c>
       <c r="R4" s="149"/>
     </row>
-    <row r="5" spans="2:18" ht="14.25" thickTop="1">
+    <row r="5" spans="2:18" ht="13.5" thickTop="1">
       <c r="B5" s="184">
         <v>1</v>
       </c>
@@ -23531,7 +24522,7 @@
       <c r="Q28" s="154"/>
       <c r="R28" s="125"/>
     </row>
-    <row r="29" spans="2:18" ht="14.25" thickBot="1">
+    <row r="29" spans="2:18" ht="13.5" thickBot="1">
       <c r="B29" s="185">
         <v>25</v>
       </c>
@@ -23553,7 +24544,7 @@
       <c r="Q29" s="152"/>
       <c r="R29" s="127"/>
     </row>
-    <row r="32" spans="2:18" ht="14.25" thickBot="1">
+    <row r="32" spans="2:18" ht="13.5" thickBot="1">
       <c r="B32" t="s">
         <v>209</v>
       </c>
@@ -23561,7 +24552,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="14.25" thickBot="1">
+    <row r="33" spans="2:18" ht="13.5" thickBot="1">
       <c r="B33" s="150" t="s">
         <v>38</v>
       </c>
@@ -23593,7 +24584,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="14.25" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="13.5" hidden="1" thickTop="1">
       <c r="B34" s="181">
         <v>0</v>
       </c>
@@ -23619,7 +24610,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="14.25" thickTop="1">
+    <row r="35" spans="2:18" ht="13.5" thickTop="1">
       <c r="B35" s="184">
         <v>1</v>
       </c>
@@ -24147,7 +25138,7 @@
       <c r="Q58" s="154"/>
       <c r="R58" s="186"/>
     </row>
-    <row r="59" spans="2:18" ht="14.25" thickBot="1">
+    <row r="59" spans="2:18" ht="13.5" thickBot="1">
       <c r="B59" s="185">
         <v>25</v>
       </c>
@@ -24198,27 +25189,27 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="28.375" customWidth="1"/>
-    <col min="3" max="3" width="15.875" customWidth="1"/>
-    <col min="5" max="5" width="12.375" customWidth="1"/>
-    <col min="6" max="6" width="19.75" customWidth="1"/>
-    <col min="7" max="7" width="12.375" customWidth="1"/>
+    <col min="2" max="2" width="28.36328125" customWidth="1"/>
+    <col min="3" max="3" width="15.90625" customWidth="1"/>
+    <col min="5" max="5" width="12.36328125" customWidth="1"/>
+    <col min="6" max="6" width="19.7265625" customWidth="1"/>
+    <col min="7" max="7" width="12.36328125" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="11" width="12.375" customWidth="1"/>
-    <col min="12" max="12" width="16.125" customWidth="1"/>
-    <col min="14" max="14" width="30.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
+    <col min="9" max="11" width="12.36328125" customWidth="1"/>
+    <col min="12" max="12" width="16.08984375" customWidth="1"/>
+    <col min="14" max="14" width="30.08984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.08984375" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="14.25" thickBot="1">
+    <row r="1" spans="2:21" ht="13.5" thickBot="1">
       <c r="C1" s="97" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="14.25" thickBot="1">
+    <row r="2" spans="2:21" ht="13.5" thickBot="1">
       <c r="B2" s="105" t="s">
         <v>62</v>
       </c>
@@ -24262,7 +25253,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="15" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="14" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="24"/>
       <c r="C3" s="55" t="s">
         <v>111</v>
@@ -24283,12 +25274,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="14.25" thickTop="1">
+    <row r="4" spans="2:21" ht="13.5" thickTop="1">
       <c r="B4" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="114" t="s">
         <v>236</v>
-      </c>
-      <c r="C4" s="114" t="s">
-        <v>237</v>
       </c>
       <c r="D4" s="121">
         <v>0</v>
@@ -24309,13 +25300,13 @@
         <v>129</v>
       </c>
       <c r="J4" s="123" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="K4" s="122" t="s">
         <v>129</v>
       </c>
       <c r="L4" s="123" t="s">
-        <v>240</v>
+        <v>31</v>
       </c>
       <c r="M4" s="56">
         <f ca="1">LEN(N4)</f>
@@ -24335,10 +25326,10 @@
     </row>
     <row r="5" spans="2:21">
       <c r="B5" s="24" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C5" s="115" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D5" s="124">
         <v>1</v>
@@ -24347,7 +25338,7 @@
         <v>129</v>
       </c>
       <c r="F5" s="125" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G5" s="24" t="s">
         <v>129</v>
@@ -24394,9 +25385,7 @@
       <c r="I6" s="24"/>
       <c r="J6" s="125"/>
       <c r="K6" s="24"/>
-      <c r="L6" s="125" t="s">
-        <v>130</v>
-      </c>
+      <c r="L6" s="125"/>
       <c r="M6" s="51" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#N/A</v>
@@ -24575,7 +25564,7 @@
       </c>
       <c r="U12" s="31"/>
     </row>
-    <row r="13" spans="2:21" ht="14.25" thickBot="1">
+    <row r="13" spans="2:21" ht="13.5" thickBot="1">
       <c r="B13" s="24"/>
       <c r="C13" s="23"/>
       <c r="D13" s="124"/>
@@ -26826,7 +27815,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="14.25" thickBot="1">
+    <row r="103" spans="2:15" ht="13.5" thickBot="1">
       <c r="B103" s="57"/>
       <c r="C103" s="58"/>
       <c r="D103" s="126"/>
@@ -26899,18 +27888,18 @@
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.125" customWidth="1"/>
+    <col min="36" max="36" width="36.36328125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.08984375" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.125" customWidth="1"/>
-    <col min="48" max="48" width="23.625" customWidth="1"/>
+    <col min="43" max="43" width="20.6328125" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.08984375" customWidth="1"/>
+    <col min="48" max="48" width="23.6328125" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -26926,7 +27915,7 @@
       <c r="B2" s="134" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="289" t="s">
+      <c r="C2" s="294" t="s">
         <v>88</v>
       </c>
       <c r="D2" s="62">
@@ -27025,7 +28014,7 @@
       <c r="AI2" s="62">
         <v>0</v>
       </c>
-      <c r="AJ2" s="291" t="s">
+      <c r="AJ2" s="296" t="s">
         <v>161</v>
       </c>
     </row>
@@ -27034,7 +28023,7 @@
         <f>IF(OR(IF(COUNTIF(D6:AC69,"0")&lt;&gt;0,TRUE,FALSE),IF(COUNTIF(D6:AC69,"1")&lt;&gt;0,TRUE,FALSE)),"Search Table","Index Table")</f>
         <v>Index Table</v>
       </c>
-      <c r="C3" s="290"/>
+      <c r="C3" s="295"/>
       <c r="D3" s="136" t="s">
         <v>65</v>
       </c>
@@ -27123,22 +28112,22 @@
         <v>66</v>
       </c>
       <c r="AG3" s="197" t="s">
-        <v>241</v>
-      </c>
-      <c r="AH3" s="297" t="s">
-        <v>272</v>
-      </c>
-      <c r="AI3" s="298"/>
-      <c r="AJ3" s="292"/>
+        <v>239</v>
+      </c>
+      <c r="AH3" s="302" t="s">
+        <v>270</v>
+      </c>
+      <c r="AI3" s="303"/>
+      <c r="AJ3" s="297"/>
       <c r="AR3" s="98" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A4" s="293" t="s">
+    <row r="4" spans="1:49" ht="13.5" thickBot="1">
+      <c r="A4" s="298" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="294"/>
+      <c r="B4" s="299"/>
       <c r="C4" s="146"/>
       <c r="D4" s="146"/>
       <c r="E4" s="146"/>
@@ -27182,9 +28171,9 @@
       <c r="AV4" s="87"/>
       <c r="AW4" s="88"/>
     </row>
-    <row r="5" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A5" s="295"/>
-      <c r="B5" s="296"/>
+    <row r="5" spans="1:49" ht="13.5" thickBot="1">
+      <c r="A5" s="300"/>
+      <c r="B5" s="301"/>
       <c r="C5" s="147"/>
       <c r="D5" s="147"/>
       <c r="E5" s="147"/>
@@ -27612,7 +28601,7 @@
         <v>0</v>
       </c>
       <c r="AJ8" s="23" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AL8" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -27632,7 +28621,7 @@
       </c>
       <c r="AU8" s="67" t="str">
         <f ca="1">IF($AW$15&lt;&gt;"NULL","        &amp;"&amp;$AW$15&amp;","&amp;REPT(" ",69-LEN($AW$15))&amp;"/* fp_vd_XDST                                         */","        vdp_PTR_NA,                                                            /* fp_vd_XDST                                         */")</f>
-        <v xml:space="preserve">        &amp;vd_s_AlertB_ledheaRwTx,                                               /* fp_vd_XDST                                         */</v>
+        <v xml:space="preserve">        vdp_PTR_NA,                                                            /* fp_vd_XDST                                         */</v>
       </c>
       <c r="AV8" s="53" t="s">
         <v>76</v>
@@ -27745,7 +28734,7 @@
         <v>1</v>
       </c>
       <c r="AJ9" s="23" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AL9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -28560,7 +29549,7 @@
       </c>
       <c r="AW15" s="72" t="str">
         <f ca="1">IF(AW6&lt;&gt;AW17,VLOOKUP(AW6,Matrix!$C$13:$G$37,5,FALSE),Matrix!G13)</f>
-        <v>vd_s_AlertB_ledheaRwTx</v>
+        <v>NULL</v>
       </c>
     </row>
     <row r="16" spans="1:49">
@@ -28693,7 +29682,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="14.25" thickBot="1">
+    <row r="17" spans="2:49" ht="13.5" thickBot="1">
       <c r="B17" s="143"/>
       <c r="C17" s="51">
         <f t="shared" si="2"/>
@@ -35063,7 +36052,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="14.25" thickBot="1">
+    <row r="70" spans="1:46" ht="13.5" thickBot="1">
       <c r="A70" s="60" t="s">
         <v>68</v>
       </c>
@@ -55690,24 +56679,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:AW118"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="35.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="3.375" customWidth="1"/>
+    <col min="2" max="2" width="35.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="3.36328125" customWidth="1"/>
     <col min="11" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="20.875" customWidth="1"/>
-    <col min="14" max="14" width="10.875" customWidth="1"/>
-    <col min="15" max="15" width="16.875" customWidth="1"/>
-    <col min="16" max="16" width="10.875" customWidth="1"/>
-    <col min="17" max="17" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.90625" customWidth="1"/>
+    <col min="14" max="14" width="10.90625" customWidth="1"/>
+    <col min="15" max="15" width="16.90625" customWidth="1"/>
+    <col min="16" max="16" width="10.90625" customWidth="1"/>
+    <col min="17" max="17" width="12.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:49" ht="15" thickBot="1">
+    <row r="2" spans="2:49" ht="14.5" thickBot="1">
       <c r="B2" s="25" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="X2" s="222" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="Y2" s="205"/>
       <c r="Z2" s="205"/>
@@ -55735,20 +56724,20 @@
       <c r="AV2" s="205"/>
       <c r="AW2" s="205"/>
     </row>
-    <row r="3" spans="2:49" ht="15" thickBot="1">
+    <row r="3" spans="2:49" ht="14.5" thickBot="1">
       <c r="B3" s="102" t="s">
         <v>164</v>
       </c>
-      <c r="C3" s="303" t="s">
+      <c r="C3" s="308" t="s">
         <v>223</v>
       </c>
-      <c r="D3" s="304"/>
-      <c r="E3" s="304"/>
-      <c r="F3" s="304"/>
-      <c r="G3" s="304"/>
-      <c r="H3" s="304"/>
-      <c r="I3" s="304"/>
-      <c r="J3" s="305"/>
+      <c r="D3" s="309"/>
+      <c r="E3" s="309"/>
+      <c r="F3" s="309"/>
+      <c r="G3" s="309"/>
+      <c r="H3" s="309"/>
+      <c r="I3" s="309"/>
+      <c r="J3" s="310"/>
       <c r="K3" s="177"/>
       <c r="L3" s="177"/>
       <c r="M3" s="180"/>
@@ -55785,22 +56774,22 @@
       <c r="B5" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="299" t="s">
+      <c r="C5" s="304" t="s">
         <v>187</v>
       </c>
-      <c r="D5" s="300"/>
-      <c r="E5" s="300"/>
-      <c r="F5" s="300"/>
-      <c r="G5" s="300"/>
-      <c r="H5" s="300"/>
-      <c r="I5" s="300"/>
-      <c r="J5" s="301"/>
+      <c r="D5" s="305"/>
+      <c r="E5" s="305"/>
+      <c r="F5" s="305"/>
+      <c r="G5" s="305"/>
+      <c r="H5" s="305"/>
+      <c r="I5" s="305"/>
+      <c r="J5" s="306"/>
       <c r="K5" s="38" t="s">
         <v>22</v>
       </c>
       <c r="L5" s="79"/>
       <c r="M5" s="31" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N5" s="28" t="s">
         <v>23</v>
@@ -55815,7 +56804,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="2:49" ht="27">
+    <row r="6" spans="2:49" ht="26">
       <c r="B6" s="75" t="s">
         <v>37</v>
       </c>
@@ -55856,38 +56845,38 @@
       <c r="O6" s="207"/>
       <c r="P6" s="83"/>
       <c r="Q6" s="216" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
-    <row r="7" spans="2:49" ht="27">
+    <row r="7" spans="2:49" ht="26">
       <c r="B7" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="302" t="s">
+      <c r="C7" s="307" t="s">
         <v>170</v>
       </c>
-      <c r="D7" s="300"/>
-      <c r="E7" s="300"/>
-      <c r="F7" s="300"/>
-      <c r="G7" s="300"/>
-      <c r="H7" s="300"/>
-      <c r="I7" s="300"/>
-      <c r="J7" s="301"/>
+      <c r="D7" s="305"/>
+      <c r="E7" s="305"/>
+      <c r="F7" s="305"/>
+      <c r="G7" s="305"/>
+      <c r="H7" s="305"/>
+      <c r="I7" s="305"/>
+      <c r="J7" s="306"/>
       <c r="K7" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="L7" s="27" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M7" s="32"/>
       <c r="N7" s="44"/>
       <c r="O7" s="207"/>
       <c r="P7" s="83"/>
       <c r="Q7" s="211" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
-    <row r="8" spans="2:49" ht="136.5">
+    <row r="8" spans="2:49" ht="131">
       <c r="B8" s="75" t="s">
         <v>28</v>
       </c>
@@ -55916,10 +56905,10 @@
         <v>177</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L8" s="27" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M8" s="31" t="s">
         <v>29</v>
@@ -55928,10 +56917,10 @@
       <c r="O8" s="207"/>
       <c r="P8" s="83"/>
       <c r="Q8" s="211" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
-    <row r="9" spans="2:49" ht="54.75" thickBot="1">
+    <row r="9" spans="2:49" ht="52.5" thickBot="1">
       <c r="B9" s="77" t="s">
         <v>30</v>
       </c>
@@ -55963,25 +56952,25 @@
         <v>219</v>
       </c>
       <c r="L9" s="26" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M9" s="33" t="s">
+        <v>246</v>
+      </c>
+      <c r="N9" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="N9" s="29" t="s">
-        <v>250</v>
-      </c>
       <c r="O9" s="223" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="P9" s="81"/>
       <c r="Q9" s="212" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
-    <row r="10" spans="2:49" ht="14.25" thickTop="1">
+    <row r="10" spans="2:49" ht="13.5" thickTop="1">
       <c r="B10" s="78" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C10" s="175" t="s">
         <v>178</v>
@@ -56020,11 +57009,11 @@
         <v>230</v>
       </c>
       <c r="O10" s="208" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="P10" s="45"/>
       <c r="Q10" s="213" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="2:49">
@@ -56068,16 +57057,16 @@
         <v>131</v>
       </c>
       <c r="O11" s="209" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="P11" s="46"/>
       <c r="Q11" s="214" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="2:49">
       <c r="B12" s="21" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C12" s="176" t="s">
         <v>178</v>
@@ -56110,22 +57099,22 @@
         <v>35</v>
       </c>
       <c r="M12" s="42" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="N12" s="43" t="s">
         <v>231</v>
       </c>
       <c r="O12" s="209" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="P12" s="46"/>
       <c r="Q12" s="214" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" spans="2:49">
       <c r="B13" s="21" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C13" s="176" t="s">
         <v>178</v>
@@ -56158,22 +57147,22 @@
         <v>36</v>
       </c>
       <c r="M13" s="42" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N13" s="43" t="s">
         <v>231</v>
       </c>
       <c r="O13" s="209" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P13" s="46"/>
       <c r="Q13" s="214" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14" spans="2:49">
       <c r="B14" s="21" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C14" s="176" t="s">
         <v>178</v>
@@ -56212,16 +57201,16 @@
         <v>31</v>
       </c>
       <c r="O14" s="209" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P14" s="46"/>
       <c r="Q14" s="214" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
-    <row r="15" spans="2:49" ht="14.25" thickBot="1">
+    <row r="15" spans="2:49" ht="13.5" thickBot="1">
       <c r="B15" s="199" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C15" s="200" t="s">
         <v>178</v>
@@ -56260,16 +57249,16 @@
         <v>31</v>
       </c>
       <c r="O15" s="210" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P15" s="204"/>
       <c r="Q15" s="215" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="69" spans="24:49">
       <c r="X69" s="222" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="Y69" s="205"/>
       <c r="Z69" s="205"/>
@@ -56299,7 +57288,7 @@
     </row>
     <row r="95" spans="24:49">
       <c r="X95" s="222" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="Y95" s="205"/>
       <c r="Z95" s="205"/>
@@ -56329,7 +57318,7 @@
     </row>
     <row r="118" spans="24:49">
       <c r="X118" s="221" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="Y118" s="205"/>
       <c r="Z118" s="205"/>
@@ -56382,14 +57371,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.25" customWidth="1"/>
+    <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="14.25" thickBot="1">
+    <row r="2" spans="2:4" ht="13.5" thickBot="1">
       <c r="B2" s="90" t="s">
         <v>89</v>
       </c>
@@ -56399,7 +57388,7 @@
       </c>
       <c r="D2" s="91"/>
     </row>
-    <row r="3" spans="2:4" ht="14.25" thickBot="1">
+    <row r="3" spans="2:4" ht="13.5" thickBot="1">
       <c r="B3" s="84" t="s">
         <v>89</v>
       </c>
@@ -56410,7 +57399,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="14.25" thickTop="1">
+    <row r="4" spans="2:4" ht="13.5" thickTop="1">
       <c r="B4" s="12">
         <v>0</v>
       </c>
@@ -56421,7 +57410,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="40.5">
+    <row r="5" spans="2:4" ht="39">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -56432,7 +57421,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="27">
+    <row r="6" spans="2:4" ht="26">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -56443,7 +57432,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="54">
+    <row r="7" spans="2:4" ht="52">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -56454,7 +57443,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="81">
+    <row r="8" spans="2:4" ht="78">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -56476,7 +57465,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="27">
+    <row r="10" spans="2:4" ht="26">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -56487,7 +57476,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="27">
+    <row r="11" spans="2:4" ht="26">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -56498,7 +57487,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="27">
+    <row r="12" spans="2:4" ht="26">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -56509,7 +57498,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="27">
+    <row r="13" spans="2:4" ht="26">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -56520,7 +57509,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="27">
+    <row r="14" spans="2:4" ht="26">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -56531,7 +57520,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="135">
+    <row r="15" spans="2:4" ht="130">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -56553,7 +57542,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="27">
+    <row r="17" spans="2:4" ht="26">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -56564,7 +57553,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="67.5">
+    <row r="18" spans="2:4" ht="91">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -56575,7 +57564,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="40.5">
+    <row r="19" spans="2:4" ht="39">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -56608,26 +57597,26 @@
         <v>212</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="27">
+    <row r="22" spans="2:4" ht="26">
       <c r="B22" s="2">
         <v>18</v>
       </c>
       <c r="C22" s="94" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D22" s="96" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="27">
+    <row r="23" spans="2:4" ht="26">
       <c r="B23" s="2">
         <v>19</v>
       </c>
       <c r="C23" s="94" t="s">
+        <v>267</v>
+      </c>
+      <c r="D23" s="96" t="s">
         <v>269</v>
-      </c>
-      <c r="D23" s="96" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="24" spans="2:4">
@@ -56645,7 +57634,7 @@
       <c r="C26" s="94"/>
       <c r="D26" s="80"/>
     </row>
-    <row r="27" spans="2:4" ht="14.25" thickBot="1">
+    <row r="27" spans="2:4" ht="13.5" thickBot="1">
       <c r="B27" s="3"/>
       <c r="C27" s="95"/>
       <c r="D27" s="5"/>

--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_LEDHEA-CSTD-1-00-A-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_LEDHEA-CSTD-1-00-A-C0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_JPlaptop\BEV_MCU\git_v043_AlertFix\src\PE1VM1\App\MET\IpcApplication\Vom\Alert\matrix\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\ソフトチーム\20260106_REMWAR_RW\045\IpcApplication\Vom\Alert\matrix\scc\ref更新\IpcApplication\Vom\Alert\matrix\scc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0C586C-F045-4367-968C-34122A6ECB61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93FD16AB-9D11-4EF5-A87B-9CD946AE69CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14535" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="1425" windowWidth="22740" windowHeight="14070" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙（承認欄）" sheetId="12" r:id="rId1"/>
@@ -674,7 +674,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2563" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2565" uniqueCount="309">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -3216,6 +3216,25 @@
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>1.2.0</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>RWの削除
+[Reference]シート
+RW記載を対象外に変更</t>
+    <rPh sb="23" eb="25">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>タイショウガイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -4691,7 +4710,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="311">
+  <cellXfs count="319">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5419,16 +5438,40 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10432,6 +10475,370 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A4BE321-B5EC-4AEA-BA82-DB0068E55548}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12584206" y="885265"/>
+          <a:ext cx="918882" cy="4157382"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="正方形/長方形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D48EA8C-5C9F-48A5-8B2C-8B224FA09A58}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13503088" y="0"/>
+          <a:ext cx="3417794" cy="1580029"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>261936</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>309562</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>71438</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="正方形/長方形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE539312-D7B6-4641-9356-D8B2468ADE57}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="26908124" y="8477250"/>
+          <a:ext cx="2119313" cy="785813"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>53</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="正方形/長方形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DA68123-8EAE-4326-AFF3-EC9ACB5343EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17716500" y="24650700"/>
+          <a:ext cx="20574000" cy="5715000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -21588,10 +21995,10 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="C1:AM57"/>
-  <sheetFormatPr defaultColWidth="8.08984375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.125" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="52" width="2.08984375" style="224" customWidth="1"/>
-    <col min="53" max="16384" width="8.08984375" style="224"/>
+    <col min="1" max="52" width="2.125" style="224" customWidth="1"/>
+    <col min="53" max="16384" width="8.125" style="224"/>
   </cols>
   <sheetData>
     <row r="1" spans="6:20" ht="13.15" customHeight="1"/>
@@ -21654,27 +22061,27 @@
       </c>
     </row>
     <row r="35" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y35" s="249" t="s">
+      <c r="Y35" s="257" t="s">
         <v>280</v>
       </c>
-      <c r="Z35" s="250"/>
-      <c r="AA35" s="250"/>
-      <c r="AB35" s="250"/>
-      <c r="AC35" s="251"/>
-      <c r="AD35" s="249" t="s">
+      <c r="Z35" s="258"/>
+      <c r="AA35" s="258"/>
+      <c r="AB35" s="258"/>
+      <c r="AC35" s="259"/>
+      <c r="AD35" s="257" t="s">
         <v>281</v>
       </c>
-      <c r="AE35" s="250"/>
-      <c r="AF35" s="250"/>
-      <c r="AG35" s="250"/>
-      <c r="AH35" s="251"/>
-      <c r="AI35" s="249" t="s">
+      <c r="AE35" s="258"/>
+      <c r="AF35" s="258"/>
+      <c r="AG35" s="258"/>
+      <c r="AH35" s="259"/>
+      <c r="AI35" s="257" t="s">
         <v>282</v>
       </c>
-      <c r="AJ35" s="250"/>
-      <c r="AK35" s="250"/>
-      <c r="AL35" s="250"/>
-      <c r="AM35" s="251"/>
+      <c r="AJ35" s="258"/>
+      <c r="AK35" s="258"/>
+      <c r="AL35" s="258"/>
+      <c r="AM35" s="259"/>
     </row>
     <row r="36" spans="3:39" ht="13.15" customHeight="1">
       <c r="D36" s="228"/>
@@ -21773,27 +22180,27 @@
       </c>
     </row>
     <row r="43" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y43" s="249" t="s">
+      <c r="Y43" s="257" t="s">
         <v>280</v>
       </c>
-      <c r="Z43" s="250"/>
-      <c r="AA43" s="250"/>
-      <c r="AB43" s="250"/>
-      <c r="AC43" s="251"/>
-      <c r="AD43" s="249" t="s">
+      <c r="Z43" s="258"/>
+      <c r="AA43" s="258"/>
+      <c r="AB43" s="258"/>
+      <c r="AC43" s="259"/>
+      <c r="AD43" s="257" t="s">
         <v>281</v>
       </c>
-      <c r="AE43" s="250"/>
-      <c r="AF43" s="250"/>
-      <c r="AG43" s="250"/>
-      <c r="AH43" s="251"/>
-      <c r="AI43" s="249" t="s">
+      <c r="AE43" s="258"/>
+      <c r="AF43" s="258"/>
+      <c r="AG43" s="258"/>
+      <c r="AH43" s="259"/>
+      <c r="AI43" s="257" t="s">
         <v>282</v>
       </c>
-      <c r="AJ43" s="250"/>
-      <c r="AK43" s="250"/>
-      <c r="AL43" s="250"/>
-      <c r="AM43" s="251"/>
+      <c r="AJ43" s="258"/>
+      <c r="AK43" s="258"/>
+      <c r="AL43" s="258"/>
+      <c r="AM43" s="259"/>
     </row>
     <row r="44" spans="3:39" ht="13.15" customHeight="1">
       <c r="D44" s="228"/>
@@ -21891,27 +22298,27 @@
       </c>
     </row>
     <row r="51" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y51" s="249" t="s">
+      <c r="Y51" s="257" t="s">
         <v>280</v>
       </c>
-      <c r="Z51" s="250"/>
-      <c r="AA51" s="250"/>
-      <c r="AB51" s="250"/>
-      <c r="AC51" s="251"/>
-      <c r="AD51" s="249" t="s">
+      <c r="Z51" s="258"/>
+      <c r="AA51" s="258"/>
+      <c r="AB51" s="258"/>
+      <c r="AC51" s="259"/>
+      <c r="AD51" s="257" t="s">
         <v>281</v>
       </c>
-      <c r="AE51" s="250"/>
-      <c r="AF51" s="250"/>
-      <c r="AG51" s="250"/>
-      <c r="AH51" s="251"/>
-      <c r="AI51" s="249" t="s">
+      <c r="AE51" s="258"/>
+      <c r="AF51" s="258"/>
+      <c r="AG51" s="258"/>
+      <c r="AH51" s="259"/>
+      <c r="AI51" s="257" t="s">
         <v>282</v>
       </c>
-      <c r="AJ51" s="250"/>
-      <c r="AK51" s="250"/>
-      <c r="AL51" s="250"/>
-      <c r="AM51" s="251"/>
+      <c r="AJ51" s="258"/>
+      <c r="AK51" s="258"/>
+      <c r="AL51" s="258"/>
+      <c r="AM51" s="259"/>
     </row>
     <row r="52" spans="4:39" ht="13.15" customHeight="1">
       <c r="D52" s="228"/>
@@ -22030,15 +22437,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:X13"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <dimension ref="B2:X14"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="4.453125" customWidth="1"/>
+    <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="9" style="9" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="69.453125" customWidth="1"/>
-    <col min="5" max="6" width="12.7265625" customWidth="1"/>
-    <col min="7" max="22" width="13.08984375" hidden="1" customWidth="1"/>
-    <col min="23" max="24" width="13.08984375" customWidth="1"/>
+    <col min="4" max="4" width="69.5" customWidth="1"/>
+    <col min="5" max="6" width="12.75" customWidth="1"/>
+    <col min="7" max="22" width="13.125" hidden="1" customWidth="1"/>
+    <col min="23" max="24" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="25.5" customHeight="1">
@@ -22049,18 +22456,18 @@
       <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="252" t="s">
+      <c r="I2" s="260" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
-      <c r="M2" s="252"/>
-      <c r="N2" s="252"/>
-      <c r="O2" s="252"/>
-      <c r="P2" s="252"/>
-      <c r="Q2" s="252"/>
-      <c r="R2" s="252"/>
+      <c r="J2" s="260"/>
+      <c r="K2" s="260"/>
+      <c r="L2" s="260"/>
+      <c r="M2" s="260"/>
+      <c r="N2" s="260"/>
+      <c r="O2" s="260"/>
+      <c r="P2" s="260"/>
+      <c r="Q2" s="260"/>
+      <c r="R2" s="260"/>
     </row>
     <row r="3" spans="2:24" ht="25.5" customHeight="1">
       <c r="C3" s="6"/>
@@ -22073,24 +22480,24 @@
       <c r="H3" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="I3" s="253" t="s">
+      <c r="I3" s="261" t="s">
         <v>218</v>
       </c>
-      <c r="J3" s="254"/>
-      <c r="K3" s="254"/>
-      <c r="L3" s="254"/>
-      <c r="M3" s="254"/>
-      <c r="N3" s="254"/>
-      <c r="O3" s="254"/>
-      <c r="P3" s="254"/>
-      <c r="Q3" s="254"/>
-      <c r="R3" s="254"/>
+      <c r="J3" s="262"/>
+      <c r="K3" s="262"/>
+      <c r="L3" s="262"/>
+      <c r="M3" s="262"/>
+      <c r="N3" s="262"/>
+      <c r="O3" s="262"/>
+      <c r="P3" s="262"/>
+      <c r="Q3" s="262"/>
+      <c r="R3" s="262"/>
     </row>
     <row r="4" spans="2:24" ht="25.5" customHeight="1">
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="22" t="str">
-        <f>DGET(B8:C14,"Ver.",H4:H5)</f>
+        <f>DGET(B8:C15,"Ver.",H4:H5)</f>
         <v>1.1.3</v>
       </c>
       <c r="F4" s="6"/>
@@ -22104,46 +22511,46 @@
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="H5" s="11">
-        <f>MAX(B9:B14)</f>
+        <f>MAX(B9:B15)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:24" ht="13.5" thickBot="1"/>
+    <row r="6" spans="2:24" ht="14.25" thickBot="1"/>
     <row r="7" spans="2:24">
-      <c r="C7" s="257" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="258"/>
-      <c r="E7" s="259" t="s">
+      <c r="C7" s="265" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="266"/>
+      <c r="E7" s="267" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="259"/>
-      <c r="G7" s="260" t="s">
+      <c r="F7" s="267"/>
+      <c r="G7" s="268" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="260"/>
-      <c r="I7" s="260"/>
-      <c r="J7" s="260"/>
-      <c r="K7" s="260"/>
-      <c r="L7" s="260"/>
-      <c r="M7" s="261" t="s">
+      <c r="H7" s="268"/>
+      <c r="I7" s="268"/>
+      <c r="J7" s="268"/>
+      <c r="K7" s="268"/>
+      <c r="L7" s="268"/>
+      <c r="M7" s="269" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="261"/>
-      <c r="O7" s="261"/>
-      <c r="P7" s="261"/>
-      <c r="Q7" s="261"/>
-      <c r="R7" s="262"/>
-      <c r="S7" s="255" t="s">
+      <c r="N7" s="269"/>
+      <c r="O7" s="269"/>
+      <c r="P7" s="269"/>
+      <c r="Q7" s="269"/>
+      <c r="R7" s="270"/>
+      <c r="S7" s="263" t="s">
         <v>294</v>
       </c>
-      <c r="T7" s="255"/>
-      <c r="U7" s="255"/>
-      <c r="V7" s="255"/>
-      <c r="W7" s="255"/>
-      <c r="X7" s="256"/>
+      <c r="T7" s="263"/>
+      <c r="U7" s="263"/>
+      <c r="V7" s="263"/>
+      <c r="W7" s="263"/>
+      <c r="X7" s="264"/>
     </row>
-    <row r="8" spans="2:24" ht="26.5" thickBot="1">
+    <row r="8" spans="2:24" ht="27.75" thickBot="1">
       <c r="B8" s="9" t="s">
         <v>15</v>
       </c>
@@ -22214,7 +22621,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:24" ht="104.5" thickTop="1">
+    <row r="9" spans="2:24" ht="108.75" thickTop="1">
       <c r="B9" s="9">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -22278,9 +22685,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="2:24" ht="130">
+    <row r="10" spans="2:24" ht="135">
       <c r="B10" s="9">
-        <f t="shared" ref="B10:B13" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
+        <f t="shared" ref="B10:B14" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -22342,7 +22749,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="2:24" ht="39">
+    <row r="11" spans="2:24" ht="40.5">
       <c r="B11" s="9">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -22394,73 +22801,101 @@
         <v>45806</v>
       </c>
     </row>
-    <row r="12" spans="2:24" ht="91">
+    <row r="12" spans="2:24" ht="94.5">
       <c r="B12" s="9">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C12" s="244" t="s">
+      <c r="C12" s="251" t="s">
         <v>303</v>
       </c>
-      <c r="D12" s="245" t="s">
+      <c r="D12" s="252" t="s">
         <v>306</v>
       </c>
-      <c r="E12" s="246" t="s">
+      <c r="E12" s="253" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="246" t="s">
+      <c r="F12" s="253" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-      <c r="T12" s="219"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="219"/>
-      <c r="W12" s="247" t="s">
+      <c r="G12" s="254"/>
+      <c r="H12" s="254"/>
+      <c r="I12" s="254"/>
+      <c r="J12" s="254"/>
+      <c r="K12" s="254"/>
+      <c r="L12" s="254"/>
+      <c r="M12" s="254"/>
+      <c r="N12" s="254"/>
+      <c r="O12" s="254"/>
+      <c r="P12" s="254"/>
+      <c r="Q12" s="254"/>
+      <c r="R12" s="254"/>
+      <c r="S12" s="254"/>
+      <c r="T12" s="255"/>
+      <c r="U12" s="254"/>
+      <c r="V12" s="255"/>
+      <c r="W12" s="254" t="s">
         <v>302</v>
       </c>
-      <c r="X12" s="248">
+      <c r="X12" s="256">
         <v>46008</v>
       </c>
     </row>
-    <row r="13" spans="2:24" ht="13.5" thickBot="1">
-      <c r="B13" s="9">
+    <row r="13" spans="2:24" ht="40.5">
+      <c r="C13" s="244" t="s">
+        <v>307</v>
+      </c>
+      <c r="D13" s="249" t="s">
+        <v>308</v>
+      </c>
+      <c r="E13" s="245"/>
+      <c r="F13" s="245"/>
+      <c r="G13" s="247"/>
+      <c r="H13" s="247"/>
+      <c r="I13" s="247"/>
+      <c r="J13" s="247"/>
+      <c r="K13" s="247"/>
+      <c r="L13" s="247"/>
+      <c r="M13" s="247"/>
+      <c r="N13" s="247"/>
+      <c r="O13" s="247"/>
+      <c r="P13" s="247"/>
+      <c r="Q13" s="247"/>
+      <c r="R13" s="247"/>
+      <c r="S13" s="247"/>
+      <c r="T13" s="248"/>
+      <c r="U13" s="247"/>
+      <c r="V13" s="248"/>
+      <c r="W13" s="250"/>
+      <c r="X13" s="246"/>
+    </row>
+    <row r="14" spans="2:24" ht="14.25" thickBot="1">
+      <c r="B14" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
-      <c r="X13" s="242"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+      <c r="X14" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -22488,11 +22923,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="4.6328125" customWidth="1"/>
-    <col min="3" max="3" width="3.453125" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" customWidth="1"/>
+    <col min="2" max="2" width="4.625" customWidth="1"/>
+    <col min="3" max="3" width="3.5" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -22506,13 +22941,13 @@
         <v>143</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="13.5" thickBot="1">
+    <row r="6" spans="2:5" ht="14.25" thickBot="1">
       <c r="B6" s="159" t="s">
         <v>134</v>
       </c>
       <c r="C6" s="159"/>
     </row>
-    <row r="7" spans="2:5" ht="13.5" thickBot="1">
+    <row r="7" spans="2:5" ht="14.25" thickBot="1">
       <c r="C7" s="84" t="s">
         <v>136</v>
       </c>
@@ -22532,7 +22967,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="26">
+    <row r="9" spans="2:5" ht="27">
       <c r="C9" s="169">
         <v>1</v>
       </c>
@@ -22543,7 +22978,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="13.5" thickBot="1">
+    <row r="10" spans="2:5" ht="14.25" thickBot="1">
       <c r="C10" s="167"/>
       <c r="D10" s="95"/>
       <c r="E10" s="5"/>
@@ -22551,14 +22986,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="165"/>
     </row>
-    <row r="12" spans="2:5" ht="13.5" thickBot="1">
+    <row r="12" spans="2:5" ht="14.25" thickBot="1">
       <c r="B12" s="160" t="s">
         <v>135</v>
       </c>
       <c r="C12" s="91"/>
       <c r="D12" s="91"/>
     </row>
-    <row r="13" spans="2:5" ht="13.5" thickBot="1">
+    <row r="13" spans="2:5" ht="14.25" thickBot="1">
       <c r="B13" s="161"/>
       <c r="C13" s="166" t="s">
         <v>136</v>
@@ -22570,7 +23005,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="13.5" thickTop="1">
+    <row r="14" spans="2:5" ht="14.25" thickTop="1">
       <c r="C14" s="163">
         <v>0</v>
       </c>
@@ -22647,17 +23082,17 @@
         <v>186</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="13.5" thickBot="1">
+    <row r="21" spans="2:5" ht="14.25" thickBot="1">
       <c r="C21" s="167"/>
       <c r="D21" s="95"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="24" spans="2:5" ht="13.5" thickBot="1">
+    <row r="24" spans="2:5" ht="14.25" thickBot="1">
       <c r="B24" s="159" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="13.5" thickBot="1">
+    <row r="25" spans="2:5" ht="14.25" thickBot="1">
       <c r="C25" s="166" t="s">
         <v>136</v>
       </c>
@@ -22744,26 +23179,26 @@
       <c r="D33" s="94"/>
       <c r="E33" s="80"/>
     </row>
-    <row r="34" spans="2:5" ht="13.5" thickBot="1">
+    <row r="34" spans="2:5" ht="14.25" thickBot="1">
       <c r="C34" s="167"/>
       <c r="D34" s="95"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="37" spans="2:5" ht="13.5" thickBot="1">
+    <row r="37" spans="2:5" ht="14.25" thickBot="1">
       <c r="B37" s="159" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="38" spans="2:5">
-      <c r="C38" s="263"/>
-      <c r="D38" s="264"/>
+      <c r="C38" s="271"/>
+      <c r="D38" s="272"/>
       <c r="E38" s="120" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="13.5" thickBot="1">
-      <c r="C39" s="265"/>
-      <c r="D39" s="266"/>
+    <row r="39" spans="2:5" ht="14.25" thickBot="1">
+      <c r="C39" s="273"/>
+      <c r="D39" s="274"/>
       <c r="E39" s="5" t="s">
         <v>122</v>
       </c>
@@ -22792,131 +23227,131 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.7265625" customWidth="1"/>
-    <col min="9" max="9" width="20.90625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.75" customWidth="1"/>
+    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="13.5" thickBot="1"/>
+    <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="292" t="s">
+      <c r="B2" s="300" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="293"/>
-      <c r="D2" s="280" t="s">
+      <c r="C2" s="301"/>
+      <c r="D2" s="288" t="s">
         <v>276</v>
       </c>
-      <c r="E2" s="281"/>
-      <c r="F2" s="281"/>
-      <c r="G2" s="281"/>
-      <c r="H2" s="282"/>
+      <c r="E2" s="289"/>
+      <c r="F2" s="289"/>
+      <c r="G2" s="289"/>
+      <c r="H2" s="290"/>
     </row>
     <row r="3" spans="2:14" ht="13.15" customHeight="1">
-      <c r="B3" s="267" t="s">
+      <c r="B3" s="275" t="s">
         <v>119</v>
       </c>
-      <c r="C3" s="268"/>
-      <c r="D3" s="283" t="s">
+      <c r="C3" s="276"/>
+      <c r="D3" s="291" t="s">
         <v>277</v>
       </c>
-      <c r="E3" s="284"/>
-      <c r="F3" s="284"/>
-      <c r="G3" s="284"/>
-      <c r="H3" s="285"/>
+      <c r="E3" s="292"/>
+      <c r="F3" s="292"/>
+      <c r="G3" s="292"/>
+      <c r="H3" s="293"/>
     </row>
-    <row r="4" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B4" s="278" t="s">
+    <row r="4" spans="2:14" ht="14.25" thickBot="1">
+      <c r="B4" s="286" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="279"/>
-      <c r="D4" s="286" t="str">
+      <c r="C4" s="287"/>
+      <c r="D4" s="294" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_B_LEDHEA-CSTD-1-00-A-C0.c</v>
       </c>
-      <c r="E4" s="287"/>
-      <c r="F4" s="287"/>
-      <c r="G4" s="287"/>
-      <c r="H4" s="288"/>
+      <c r="E4" s="295"/>
+      <c r="F4" s="295"/>
+      <c r="G4" s="295"/>
+      <c r="H4" s="296"/>
     </row>
-    <row r="5" spans="2:14" ht="13.5" thickBot="1">
+    <row r="5" spans="2:14" ht="14.25" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="292" t="s">
+      <c r="B6" s="300" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="293"/>
-      <c r="D6" s="289" t="str">
+      <c r="C6" s="301"/>
+      <c r="D6" s="297" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>B_LEDHEA</v>
       </c>
-      <c r="E6" s="290"/>
-      <c r="F6" s="290"/>
-      <c r="G6" s="290"/>
-      <c r="H6" s="291"/>
+      <c r="E6" s="298"/>
+      <c r="F6" s="298"/>
+      <c r="G6" s="298"/>
+      <c r="H6" s="299"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="267" t="s">
+      <c r="B7" s="275" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="268"/>
-      <c r="D7" s="269">
+      <c r="C7" s="276"/>
+      <c r="D7" s="277">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="270"/>
-      <c r="F7" s="270"/>
-      <c r="G7" s="270"/>
-      <c r="H7" s="271"/>
+      <c r="E7" s="278"/>
+      <c r="F7" s="278"/>
+      <c r="G7" s="278"/>
+      <c r="H7" s="279"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="267" t="s">
+      <c r="B8" s="275" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="268"/>
-      <c r="D8" s="269" t="str">
+      <c r="C8" s="276"/>
+      <c r="D8" s="277" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_B_LEDHEA_MTRX</v>
       </c>
-      <c r="E8" s="270"/>
-      <c r="F8" s="270"/>
-      <c r="G8" s="270"/>
-      <c r="H8" s="271"/>
+      <c r="E8" s="278"/>
+      <c r="F8" s="278"/>
+      <c r="G8" s="278"/>
+      <c r="H8" s="279"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="267" t="s">
+      <c r="B9" s="275" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="268"/>
-      <c r="D9" s="272" t="s">
+      <c r="C9" s="276"/>
+      <c r="D9" s="280" t="s">
         <v>225</v>
       </c>
-      <c r="E9" s="273"/>
-      <c r="F9" s="273"/>
-      <c r="G9" s="273"/>
-      <c r="H9" s="274"/>
+      <c r="E9" s="281"/>
+      <c r="F9" s="281"/>
+      <c r="G9" s="281"/>
+      <c r="H9" s="282"/>
     </row>
-    <row r="10" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B10" s="278" t="s">
+    <row r="10" spans="2:14" ht="14.25" thickBot="1">
+      <c r="B10" s="286" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="279"/>
-      <c r="D10" s="275"/>
-      <c r="E10" s="276"/>
-      <c r="F10" s="276"/>
-      <c r="G10" s="276"/>
-      <c r="H10" s="277"/>
+      <c r="C10" s="287"/>
+      <c r="D10" s="283"/>
+      <c r="E10" s="284"/>
+      <c r="F10" s="284"/>
+      <c r="G10" s="284"/>
+      <c r="H10" s="285"/>
     </row>
-    <row r="11" spans="2:14" ht="13.5" thickBot="1"/>
-    <row r="12" spans="2:14" ht="13.5" thickBot="1">
+    <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
+    <row r="12" spans="2:14" ht="14.25" thickBot="1">
       <c r="B12" s="150" t="s">
         <v>38</v>
       </c>
@@ -22951,7 +23386,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="13.5" thickTop="1">
+    <row r="13" spans="2:14" ht="14.25" thickTop="1">
       <c r="B13" s="113">
         <v>1</v>
       </c>
@@ -23804,7 +24239,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="13.5" thickBot="1">
+    <row r="37" spans="2:14" ht="14.25" thickBot="1">
       <c r="B37" s="104">
         <v>25</v>
       </c>
@@ -23906,21 +24341,21 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.453125" customWidth="1"/>
-    <col min="6" max="6" width="52.7265625" customWidth="1"/>
-    <col min="7" max="7" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.90625" customWidth="1"/>
-    <col min="16" max="16" width="9.90625" customWidth="1"/>
-    <col min="17" max="17" width="44.6328125" customWidth="1"/>
-    <col min="18" max="18" width="73.6328125" customWidth="1"/>
+    <col min="5" max="5" width="36.5" customWidth="1"/>
+    <col min="6" max="6" width="52.75" customWidth="1"/>
+    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.875" customWidth="1"/>
+    <col min="16" max="16" width="9.875" customWidth="1"/>
+    <col min="17" max="17" width="44.625" customWidth="1"/>
+    <col min="18" max="18" width="73.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="13.5" thickBot="1">
+    <row r="2" spans="2:18" ht="14.25" thickBot="1">
       <c r="B2" t="s">
         <v>208</v>
       </c>
@@ -23928,7 +24363,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="13.5" thickBot="1">
+    <row r="3" spans="2:18" ht="14.25" thickBot="1">
       <c r="B3" s="150" t="s">
         <v>38</v>
       </c>
@@ -23966,7 +24401,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="14.25" hidden="1" thickTop="1">
       <c r="B4" s="181">
         <v>0</v>
       </c>
@@ -23994,7 +24429,7 @@
       </c>
       <c r="R4" s="149"/>
     </row>
-    <row r="5" spans="2:18" ht="13.5" thickTop="1">
+    <row r="5" spans="2:18" ht="14.25" thickTop="1">
       <c r="B5" s="184">
         <v>1</v>
       </c>
@@ -24522,7 +24957,7 @@
       <c r="Q28" s="154"/>
       <c r="R28" s="125"/>
     </row>
-    <row r="29" spans="2:18" ht="13.5" thickBot="1">
+    <row r="29" spans="2:18" ht="14.25" thickBot="1">
       <c r="B29" s="185">
         <v>25</v>
       </c>
@@ -24544,7 +24979,7 @@
       <c r="Q29" s="152"/>
       <c r="R29" s="127"/>
     </row>
-    <row r="32" spans="2:18" ht="13.5" thickBot="1">
+    <row r="32" spans="2:18" ht="14.25" thickBot="1">
       <c r="B32" t="s">
         <v>209</v>
       </c>
@@ -24552,7 +24987,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="13.5" thickBot="1">
+    <row r="33" spans="2:18" ht="14.25" thickBot="1">
       <c r="B33" s="150" t="s">
         <v>38</v>
       </c>
@@ -24584,7 +25019,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="14.25" hidden="1" thickTop="1">
       <c r="B34" s="181">
         <v>0</v>
       </c>
@@ -24610,7 +25045,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="13.5" thickTop="1">
+    <row r="35" spans="2:18" ht="14.25" thickTop="1">
       <c r="B35" s="184">
         <v>1</v>
       </c>
@@ -25138,7 +25573,7 @@
       <c r="Q58" s="154"/>
       <c r="R58" s="186"/>
     </row>
-    <row r="59" spans="2:18" ht="13.5" thickBot="1">
+    <row r="59" spans="2:18" ht="14.25" thickBot="1">
       <c r="B59" s="185">
         <v>25</v>
       </c>
@@ -25189,27 +25624,27 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="28.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.90625" customWidth="1"/>
-    <col min="5" max="5" width="12.36328125" customWidth="1"/>
-    <col min="6" max="6" width="19.7265625" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" customWidth="1"/>
+    <col min="2" max="2" width="28.375" customWidth="1"/>
+    <col min="3" max="3" width="15.875" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="19.75" customWidth="1"/>
+    <col min="7" max="7" width="12.375" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="11" width="12.36328125" customWidth="1"/>
-    <col min="12" max="12" width="16.08984375" customWidth="1"/>
-    <col min="14" max="14" width="30.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.08984375" hidden="1" customWidth="1"/>
+    <col min="9" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="16.125" customWidth="1"/>
+    <col min="14" max="14" width="30.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="13.5" thickBot="1">
+    <row r="1" spans="2:21" ht="14.25" thickBot="1">
       <c r="C1" s="97" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="13.5" thickBot="1">
+    <row r="2" spans="2:21" ht="14.25" thickBot="1">
       <c r="B2" s="105" t="s">
         <v>62</v>
       </c>
@@ -25253,7 +25688,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="14" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="15" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="24"/>
       <c r="C3" s="55" t="s">
         <v>111</v>
@@ -25274,7 +25709,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="13.5" thickTop="1">
+    <row r="4" spans="2:21" ht="14.25" thickTop="1">
       <c r="B4" s="24" t="s">
         <v>235</v>
       </c>
@@ -25564,7 +25999,7 @@
       </c>
       <c r="U12" s="31"/>
     </row>
-    <row r="13" spans="2:21" ht="13.5" thickBot="1">
+    <row r="13" spans="2:21" ht="14.25" thickBot="1">
       <c r="B13" s="24"/>
       <c r="C13" s="23"/>
       <c r="D13" s="124"/>
@@ -27815,7 +28250,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="13.5" thickBot="1">
+    <row r="103" spans="2:15" ht="14.25" thickBot="1">
       <c r="B103" s="57"/>
       <c r="C103" s="58"/>
       <c r="D103" s="126"/>
@@ -27888,18 +28323,18 @@
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.36328125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.08984375" customWidth="1"/>
+    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.125" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.6328125" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.08984375" customWidth="1"/>
-    <col min="48" max="48" width="23.6328125" customWidth="1"/>
+    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.125" customWidth="1"/>
+    <col min="48" max="48" width="23.625" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -27915,7 +28350,7 @@
       <c r="B2" s="134" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="294" t="s">
+      <c r="C2" s="302" t="s">
         <v>88</v>
       </c>
       <c r="D2" s="62">
@@ -28014,7 +28449,7 @@
       <c r="AI2" s="62">
         <v>0</v>
       </c>
-      <c r="AJ2" s="296" t="s">
+      <c r="AJ2" s="304" t="s">
         <v>161</v>
       </c>
     </row>
@@ -28023,7 +28458,7 @@
         <f>IF(OR(IF(COUNTIF(D6:AC69,"0")&lt;&gt;0,TRUE,FALSE),IF(COUNTIF(D6:AC69,"1")&lt;&gt;0,TRUE,FALSE)),"Search Table","Index Table")</f>
         <v>Index Table</v>
       </c>
-      <c r="C3" s="295"/>
+      <c r="C3" s="303"/>
       <c r="D3" s="136" t="s">
         <v>65</v>
       </c>
@@ -28114,20 +28549,20 @@
       <c r="AG3" s="197" t="s">
         <v>239</v>
       </c>
-      <c r="AH3" s="302" t="s">
+      <c r="AH3" s="310" t="s">
         <v>270</v>
       </c>
-      <c r="AI3" s="303"/>
-      <c r="AJ3" s="297"/>
+      <c r="AI3" s="311"/>
+      <c r="AJ3" s="305"/>
       <c r="AR3" s="98" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="13.5" thickBot="1">
-      <c r="A4" s="298" t="s">
+    <row r="4" spans="1:49" ht="14.25" thickBot="1">
+      <c r="A4" s="306" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="299"/>
+      <c r="B4" s="307"/>
       <c r="C4" s="146"/>
       <c r="D4" s="146"/>
       <c r="E4" s="146"/>
@@ -28171,9 +28606,9 @@
       <c r="AV4" s="87"/>
       <c r="AW4" s="88"/>
     </row>
-    <row r="5" spans="1:49" ht="13.5" thickBot="1">
-      <c r="A5" s="300"/>
-      <c r="B5" s="301"/>
+    <row r="5" spans="1:49" ht="14.25" thickBot="1">
+      <c r="A5" s="308"/>
+      <c r="B5" s="309"/>
       <c r="C5" s="147"/>
       <c r="D5" s="147"/>
       <c r="E5" s="147"/>
@@ -29682,7 +30117,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="13.5" thickBot="1">
+    <row r="17" spans="2:49" ht="14.25" thickBot="1">
       <c r="B17" s="143"/>
       <c r="C17" s="51">
         <f t="shared" si="2"/>
@@ -36052,7 +36487,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="13.5" thickBot="1">
+    <row r="70" spans="1:46" ht="14.25" thickBot="1">
       <c r="A70" s="60" t="s">
         <v>68</v>
       </c>
@@ -56679,19 +57114,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:AW118"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="35.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="3.36328125" customWidth="1"/>
+    <col min="2" max="2" width="35.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="3.375" customWidth="1"/>
     <col min="11" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="20.90625" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" customWidth="1"/>
-    <col min="15" max="15" width="16.90625" customWidth="1"/>
-    <col min="16" max="16" width="10.90625" customWidth="1"/>
-    <col min="17" max="17" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.875" customWidth="1"/>
+    <col min="14" max="14" width="10.875" customWidth="1"/>
+    <col min="15" max="15" width="16.875" customWidth="1"/>
+    <col min="16" max="16" width="10.875" customWidth="1"/>
+    <col min="17" max="17" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:49" ht="14.5" thickBot="1">
+    <row r="2" spans="2:49" ht="15" thickBot="1">
       <c r="B2" s="25" t="s">
         <v>274</v>
       </c>
@@ -56724,20 +57159,20 @@
       <c r="AV2" s="205"/>
       <c r="AW2" s="205"/>
     </row>
-    <row r="3" spans="2:49" ht="14.5" thickBot="1">
+    <row r="3" spans="2:49" ht="15" thickBot="1">
       <c r="B3" s="102" t="s">
         <v>164</v>
       </c>
-      <c r="C3" s="308" t="s">
+      <c r="C3" s="316" t="s">
         <v>223</v>
       </c>
-      <c r="D3" s="309"/>
-      <c r="E3" s="309"/>
-      <c r="F3" s="309"/>
-      <c r="G3" s="309"/>
-      <c r="H3" s="309"/>
-      <c r="I3" s="309"/>
-      <c r="J3" s="310"/>
+      <c r="D3" s="317"/>
+      <c r="E3" s="317"/>
+      <c r="F3" s="317"/>
+      <c r="G3" s="317"/>
+      <c r="H3" s="317"/>
+      <c r="I3" s="317"/>
+      <c r="J3" s="318"/>
       <c r="K3" s="177"/>
       <c r="L3" s="177"/>
       <c r="M3" s="180"/>
@@ -56774,16 +57209,16 @@
       <c r="B5" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="304" t="s">
+      <c r="C5" s="312" t="s">
         <v>187</v>
       </c>
-      <c r="D5" s="305"/>
-      <c r="E5" s="305"/>
-      <c r="F5" s="305"/>
-      <c r="G5" s="305"/>
-      <c r="H5" s="305"/>
-      <c r="I5" s="305"/>
-      <c r="J5" s="306"/>
+      <c r="D5" s="313"/>
+      <c r="E5" s="313"/>
+      <c r="F5" s="313"/>
+      <c r="G5" s="313"/>
+      <c r="H5" s="313"/>
+      <c r="I5" s="313"/>
+      <c r="J5" s="314"/>
       <c r="K5" s="38" t="s">
         <v>22</v>
       </c>
@@ -56804,7 +57239,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="2:49" ht="26">
+    <row r="6" spans="2:49" ht="27">
       <c r="B6" s="75" t="s">
         <v>37</v>
       </c>
@@ -56848,20 +57283,20 @@
         <v>266</v>
       </c>
     </row>
-    <row r="7" spans="2:49" ht="26">
+    <row r="7" spans="2:49" ht="27">
       <c r="B7" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="307" t="s">
+      <c r="C7" s="315" t="s">
         <v>170</v>
       </c>
-      <c r="D7" s="305"/>
-      <c r="E7" s="305"/>
-      <c r="F7" s="305"/>
-      <c r="G7" s="305"/>
-      <c r="H7" s="305"/>
-      <c r="I7" s="305"/>
-      <c r="J7" s="306"/>
+      <c r="D7" s="313"/>
+      <c r="E7" s="313"/>
+      <c r="F7" s="313"/>
+      <c r="G7" s="313"/>
+      <c r="H7" s="313"/>
+      <c r="I7" s="313"/>
+      <c r="J7" s="314"/>
       <c r="K7" s="1" t="s">
         <v>243</v>
       </c>
@@ -56876,7 +57311,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="8" spans="2:49" ht="131">
+    <row r="8" spans="2:49" ht="136.5">
       <c r="B8" s="75" t="s">
         <v>28</v>
       </c>
@@ -56920,7 +57355,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="9" spans="2:49" ht="52.5" thickBot="1">
+    <row r="9" spans="2:49" ht="54.75" thickBot="1">
       <c r="B9" s="77" t="s">
         <v>30</v>
       </c>
@@ -56968,7 +57403,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="10" spans="2:49" ht="13.5" thickTop="1">
+    <row r="10" spans="2:49" ht="14.25" thickTop="1">
       <c r="B10" s="78" t="s">
         <v>251</v>
       </c>
@@ -57208,7 +57643,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="15" spans="2:49" ht="13.5" thickBot="1">
+    <row r="15" spans="2:49" ht="14.25" thickBot="1">
       <c r="B15" s="199" t="s">
         <v>257</v>
       </c>
@@ -57371,14 +57806,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="13.5" thickBot="1">
+    <row r="2" spans="2:4" ht="14.25" thickBot="1">
       <c r="B2" s="90" t="s">
         <v>89</v>
       </c>
@@ -57388,7 +57823,7 @@
       </c>
       <c r="D2" s="91"/>
     </row>
-    <row r="3" spans="2:4" ht="13.5" thickBot="1">
+    <row r="3" spans="2:4" ht="14.25" thickBot="1">
       <c r="B3" s="84" t="s">
         <v>89</v>
       </c>
@@ -57399,7 +57834,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="13.5" thickTop="1">
+    <row r="4" spans="2:4" ht="14.25" thickTop="1">
       <c r="B4" s="12">
         <v>0</v>
       </c>
@@ -57410,7 +57845,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="39">
+    <row r="5" spans="2:4" ht="40.5">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -57421,7 +57856,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="26">
+    <row r="6" spans="2:4" ht="27">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -57432,7 +57867,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="52">
+    <row r="7" spans="2:4" ht="54">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -57443,7 +57878,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="78">
+    <row r="8" spans="2:4" ht="81">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -57465,7 +57900,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="26">
+    <row r="10" spans="2:4" ht="27">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -57476,7 +57911,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="26">
+    <row r="11" spans="2:4" ht="27">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -57487,7 +57922,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="26">
+    <row r="12" spans="2:4" ht="27">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -57498,7 +57933,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="26">
+    <row r="13" spans="2:4" ht="27">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -57509,7 +57944,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="26">
+    <row r="14" spans="2:4" ht="27">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -57520,7 +57955,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="130">
+    <row r="15" spans="2:4" ht="135">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -57542,7 +57977,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="26">
+    <row r="17" spans="2:4" ht="27">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -57553,7 +57988,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="91">
+    <row r="18" spans="2:4" ht="67.5">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -57564,7 +57999,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="39">
+    <row r="19" spans="2:4" ht="40.5">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -57597,7 +58032,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="26">
+    <row r="22" spans="2:4" ht="27">
       <c r="B22" s="2">
         <v>18</v>
       </c>
@@ -57608,7 +58043,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="26">
+    <row r="23" spans="2:4" ht="27">
       <c r="B23" s="2">
         <v>19</v>
       </c>
@@ -57634,7 +58069,7 @@
       <c r="C26" s="94"/>
       <c r="D26" s="80"/>
     </row>
-    <row r="27" spans="2:4" ht="13.5" thickBot="1">
+    <row r="27" spans="2:4" ht="14.25" thickBot="1">
       <c r="B27" s="3"/>
       <c r="C27" s="95"/>
       <c r="D27" s="5"/>
